--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -545,13 +545,13 @@
     <t>1002</t>
   </si>
   <si>
-    <t>刺杀剑术·祝福</t>
+    <t>穿刺剑术·祝福</t>
   </si>
   <si>
     <t>10004</t>
   </si>
   <si>
-    <t>刺杀剑术·致命</t>
+    <t>穿刺剑术·致命</t>
   </si>
   <si>
     <t>10005</t>
@@ -560,13 +560,13 @@
     <t>1003</t>
   </si>
   <si>
-    <t>半月弯刀·祝福</t>
+    <t>圆月弯刀·祝福</t>
   </si>
   <si>
     <t>10006</t>
   </si>
   <si>
-    <t>半月弯刀·致命</t>
+    <t>圆月弯刀·致命</t>
   </si>
   <si>
     <t>10007</t>
@@ -575,13 +575,13 @@
     <t>1004</t>
   </si>
   <si>
-    <t>野蛮撞击·祝福</t>
+    <t>蛮力撞击·祝福</t>
   </si>
   <si>
     <t>10008</t>
   </si>
   <si>
-    <t>野蛮撞击·致命</t>
+    <t>蛮力撞击·致命</t>
   </si>
   <si>
     <t>10009</t>
@@ -620,13 +620,13 @@
     <t>1007</t>
   </si>
   <si>
-    <t>烈火剑法·祝福</t>
+    <t>火焰剑法·祝福</t>
   </si>
   <si>
     <t>10014</t>
   </si>
   <si>
-    <t>烈火剑法·致命</t>
+    <t>火焰剑法·致命</t>
   </si>
   <si>
     <t>10015</t>
@@ -635,13 +635,13 @@
     <t>2001</t>
   </si>
   <si>
-    <t>小火球·祝福</t>
+    <t>火球术·祝福</t>
   </si>
   <si>
     <t>10016</t>
   </si>
   <si>
-    <t>小火球·致命</t>
+    <t>火球术·致命</t>
   </si>
   <si>
     <t>10017</t>
@@ -650,13 +650,13 @@
     <t>2002</t>
   </si>
   <si>
-    <t>雷电术·祝福</t>
+    <t>神雷术·祝福</t>
   </si>
   <si>
     <t>10018</t>
   </si>
   <si>
-    <t>雷电术·致命</t>
+    <t>神雷术·致命</t>
   </si>
   <si>
     <t>10019</t>
@@ -680,13 +680,13 @@
     <t>2004</t>
   </si>
   <si>
-    <t>爆裂火焰·祝福</t>
+    <t>火焰术·祝福</t>
   </si>
   <si>
     <t>10022</t>
   </si>
   <si>
-    <t>爆裂火焰·致命</t>
+    <t>火焰术·致命</t>
   </si>
   <si>
     <t>10023</t>
@@ -716,13 +716,13 @@
     <t>2007</t>
   </si>
   <si>
-    <t>冰咆哮·祝福</t>
+    <t>冰冻术·祝福</t>
   </si>
   <si>
     <t>10028</t>
   </si>
   <si>
-    <t>冰咆哮·致命</t>
+    <t>冰冻术·致命</t>
   </si>
   <si>
     <t>10029</t>
@@ -731,13 +731,13 @@
     <t>3001</t>
   </si>
   <si>
-    <t>治疗术·祝福</t>
+    <t>治疗道法·祝福</t>
   </si>
   <si>
     <t>10030</t>
   </si>
   <si>
-    <t>治疗术·强化</t>
+    <t>治疗道法·强化</t>
   </si>
   <si>
     <t>技能提高50%技能系数</t>
@@ -749,13 +749,13 @@
     <t>3002</t>
   </si>
   <si>
-    <t>火符术·祝福</t>
+    <t>火符道法·祝福</t>
   </si>
   <si>
     <t>10032</t>
   </si>
   <si>
-    <t>火符术·致命</t>
+    <t>火符道法·致命</t>
   </si>
   <si>
     <t>10033</t>
@@ -764,13 +764,13 @@
     <t>3003</t>
   </si>
   <si>
-    <t>施毒术·祝福</t>
+    <t>毒咒道法·祝福</t>
   </si>
   <si>
     <t>10034</t>
   </si>
   <si>
-    <t>施毒术·致命</t>
+    <t>毒咒道法·致命</t>
   </si>
   <si>
     <t>10035</t>
@@ -779,13 +779,13 @@
     <t>3004</t>
   </si>
   <si>
-    <t>召唤骷髅·祝福</t>
+    <t>召唤金刚·祝福</t>
   </si>
   <si>
     <t>10036</t>
   </si>
   <si>
-    <t>召唤骷髅·传承</t>
+    <t>召唤金刚·传承</t>
   </si>
   <si>
     <t>骷髅增加20%高级属性继承</t>
@@ -818,13 +818,13 @@
     <t>3007</t>
   </si>
   <si>
-    <t>召唤神兽·祝福</t>
+    <t>召唤魔兽·祝福</t>
   </si>
   <si>
     <t>10042</t>
   </si>
   <si>
-    <t>召唤神兽·传承</t>
+    <t>召唤魔兽·传承</t>
   </si>
   <si>
     <t>神兽增加20%高级属性继承</t>
@@ -842,13 +842,13 @@
     <t>增加一个持续4回合100%灼烧效果</t>
   </si>
   <si>
-    <t>治疗术·回复</t>
+    <t>治疗道法·回复</t>
   </si>
   <si>
     <t>增加一个持续4回合100%回复效果</t>
   </si>
   <si>
-    <t>火符术·中毒</t>
+    <t>火符道法·中毒</t>
   </si>
   <si>
     <t>增加一个持续4回合50%中毒效果</t>
@@ -860,7 +860,7 @@
     <t>使目标附加50%的伤害,叠加3层,持续4s</t>
   </si>
   <si>
-    <t>冰咆哮·冰封</t>
+    <t>冰冻术·冰封</t>
   </si>
   <si>
     <t>增加2S冰冻时间</t>
@@ -878,16 +878,16 @@
     <t>道力精通·祝福</t>
   </si>
   <si>
-    <t>刺杀剑术·吸血</t>
-  </si>
-  <si>
-    <t>冰咆哮·哀霜</t>
+    <t>穿刺剑术·吸血</t>
+  </si>
+  <si>
+    <t>冰冻术·哀霜</t>
   </si>
   <si>
     <t>使敌人受到的伤害增加30%，持续5秒</t>
   </si>
   <si>
-    <t>烈火剑法·血怒</t>
+    <t>火焰剑法·血怒</t>
   </si>
   <si>
     <t>必定暴击</t>
@@ -899,31 +899,31 @@
     <t>回血比例增加1%</t>
   </si>
   <si>
-    <t>瞬息移动·叠浪</t>
+    <t>闪烁术·叠浪</t>
   </si>
   <si>
     <t>魔法伤害加成增加3次叠加层数</t>
   </si>
   <si>
-    <t>隐身术·持久</t>
+    <t>隐身道法·持久</t>
   </si>
   <si>
     <t>隐身持续时间增加3秒</t>
   </si>
   <si>
-    <t>开天斩·强化</t>
+    <t>开天辟地·强化</t>
   </si>
   <si>
     <t>造成的比例伤害,增加3%</t>
   </si>
   <si>
-    <t>流星火雨·穿透</t>
-  </si>
-  <si>
-    <t>流星火雨无视50%护甲</t>
-  </si>
-  <si>
-    <t>召唤月灵·复制</t>
+    <t>火雨术·穿透</t>
+  </si>
+  <si>
+    <t>火雨术无视50%护甲</t>
+  </si>
+  <si>
+    <t>召唤护法·复制</t>
   </si>
   <si>
     <t>月灵数量+2</t>
@@ -947,13 +947,13 @@
     <t>提高此技能系数50%倍率</t>
   </si>
   <si>
-    <t>刺杀剑术·觉醒</t>
-  </si>
-  <si>
-    <t>半月弯刀·觉醒</t>
-  </si>
-  <si>
-    <t>野蛮撞击·觉醒</t>
+    <t>穿刺剑术·觉醒</t>
+  </si>
+  <si>
+    <t>圆月弯刀·觉醒</t>
+  </si>
+  <si>
+    <t>蛮力撞击·觉醒</t>
   </si>
   <si>
     <t>武力盾·觉醒</t>
@@ -962,16 +962,16 @@
     <t>武力精通·觉醒</t>
   </si>
   <si>
-    <t>烈火剑法·觉醒</t>
+    <t>火焰剑法·觉醒</t>
   </si>
   <si>
     <t>护体神盾·觉醒</t>
   </si>
   <si>
-    <t>开天斩·觉醒</t>
-  </si>
-  <si>
-    <t>彻地钉·觉醒</t>
+    <t>开天辟地·觉醒</t>
+  </si>
+  <si>
+    <t>地刺术·觉醒</t>
   </si>
   <si>
     <t>#</t>
@@ -980,22 +980,22 @@
     <t>战士之魂·觉醒</t>
   </si>
   <si>
-    <t>彻地钉·大大大</t>
+    <t>地刺术·大大大</t>
   </si>
   <si>
     <t>增加一圈攻击范围</t>
   </si>
   <si>
-    <t>小火球·觉醒</t>
-  </si>
-  <si>
-    <t>雷电术·觉醒</t>
+    <t>火球术·觉醒</t>
+  </si>
+  <si>
+    <t>神雷术·觉醒</t>
   </si>
   <si>
     <t>火墙·觉醒</t>
   </si>
   <si>
-    <t>爆裂火焰·觉醒</t>
+    <t>火焰术·觉醒</t>
   </si>
   <si>
     <t>魔法盾·觉醒</t>
@@ -1004,13 +1004,13 @@
     <t>法术精通·觉醒</t>
   </si>
   <si>
-    <t>冰咆哮·觉醒</t>
-  </si>
-  <si>
-    <t>瞬息移动·觉醒</t>
-  </si>
-  <si>
-    <t>流星火雨·觉醒</t>
+    <t>冰冻术·觉醒</t>
+  </si>
+  <si>
+    <t>闪烁术·觉醒</t>
+  </si>
+  <si>
+    <t>火雨术·觉醒</t>
   </si>
   <si>
     <t>分身术·觉醒</t>
@@ -1025,16 +1025,16 @@
     <t>提高15S持续时间</t>
   </si>
   <si>
-    <t>治疗术·觉醒</t>
-  </si>
-  <si>
-    <t>火符术·觉醒</t>
-  </si>
-  <si>
-    <t>施毒术·觉醒</t>
-  </si>
-  <si>
-    <t>召唤骷髅·觉醒</t>
+    <t>治疗道法·觉醒</t>
+  </si>
+  <si>
+    <t>火符道法·觉醒</t>
+  </si>
+  <si>
+    <t>毒咒道法·觉醒</t>
+  </si>
+  <si>
+    <t>召唤金刚·觉醒</t>
   </si>
   <si>
     <t>道力盾·觉醒</t>
@@ -1043,13 +1043,13 @@
     <t>道力精通·觉醒</t>
   </si>
   <si>
-    <t>召唤神兽·觉醒</t>
-  </si>
-  <si>
-    <t>隐身术·觉醒</t>
-  </si>
-  <si>
-    <t>召唤月灵·觉醒</t>
+    <t>召唤魔兽·觉醒</t>
+  </si>
+  <si>
+    <t>隐身道法·觉醒</t>
+  </si>
+  <si>
+    <t>召唤护法·觉醒</t>
   </si>
   <si>
     <t>无极道体·觉醒</t>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -779,13 +779,13 @@
     <t>3004</t>
   </si>
   <si>
-    <t>召唤金刚·祝福</t>
+    <t>召唤小兵·祝福</t>
   </si>
   <si>
     <t>10036</t>
   </si>
   <si>
-    <t>召唤金刚·传承</t>
+    <t>召唤小兵·传承</t>
   </si>
   <si>
     <t>骷髅增加20%高级属性继承</t>
@@ -923,10 +923,10 @@
     <t>火雨术无视50%护甲</t>
   </si>
   <si>
-    <t>召唤护法·复制</t>
-  </si>
-  <si>
-    <t>月灵数量+2</t>
+    <t>召唤月神·复制</t>
+  </si>
+  <si>
+    <t>月神数量+2</t>
   </si>
   <si>
     <t>此技能ID</t>
@@ -1034,7 +1034,7 @@
     <t>毒咒道法·觉醒</t>
   </si>
   <si>
-    <t>召唤金刚·觉醒</t>
+    <t>召唤小兵·觉醒</t>
   </si>
   <si>
     <t>道力盾·觉醒</t>
@@ -1049,7 +1049,7 @@
     <t>隐身道法·觉醒</t>
   </si>
   <si>
-    <t>召唤护法·觉醒</t>
+    <t>召唤月神·觉醒</t>
   </si>
   <si>
     <t>无极道体·觉醒</t>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -695,13 +695,13 @@
     <t>2005</t>
   </si>
   <si>
-    <t>魔法盾·生命</t>
+    <t>法力盾·生命</t>
   </si>
   <si>
     <t>10024</t>
   </si>
   <si>
-    <t>魔法盾·防御</t>
+    <t>法力盾·防御</t>
   </si>
   <si>
     <t>10025</t>
@@ -899,7 +899,7 @@
     <t>回血比例增加1%</t>
   </si>
   <si>
-    <t>闪烁术·叠浪</t>
+    <t>瞬移术·叠浪</t>
   </si>
   <si>
     <t>魔法伤害加成增加3次叠加层数</t>
@@ -998,7 +998,7 @@
     <t>火焰术·觉醒</t>
   </si>
   <si>
-    <t>魔法盾·觉醒</t>
+    <t>法力盾·觉醒</t>
   </si>
   <si>
     <t>法术精通·觉醒</t>
@@ -1007,7 +1007,7 @@
     <t>冰冻术·觉醒</t>
   </si>
   <si>
-    <t>闪烁术·觉醒</t>
+    <t>瞬移术·觉醒</t>
   </si>
   <si>
     <t>火雨术·觉醒</t>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -545,13 +545,13 @@
     <t>1002</t>
   </si>
   <si>
-    <t>穿刺剑术·祝福</t>
+    <t>流光剑法·祝福</t>
   </si>
   <si>
     <t>10004</t>
   </si>
   <si>
-    <t>穿刺剑术·致命</t>
+    <t>流光剑法·致命</t>
   </si>
   <si>
     <t>10005</t>
@@ -560,13 +560,13 @@
     <t>1003</t>
   </si>
   <si>
-    <t>圆月弯刀·祝福</t>
+    <t>旋风斩·祝福</t>
   </si>
   <si>
     <t>10006</t>
   </si>
   <si>
-    <t>圆月弯刀·致命</t>
+    <t>旋风斩·致命</t>
   </si>
   <si>
     <t>10007</t>
@@ -590,13 +590,13 @@
     <t>1005</t>
   </si>
   <si>
-    <t>武力盾·生命</t>
+    <t>武神盾·生命</t>
   </si>
   <si>
     <t>技能提高50%生命加成</t>
   </si>
   <si>
-    <t>武力盾·防御</t>
+    <t>武神盾·防御</t>
   </si>
   <si>
     <t>技能提高50%防御加成</t>
@@ -620,13 +620,13 @@
     <t>1007</t>
   </si>
   <si>
-    <t>火焰剑法·祝福</t>
+    <t>烈焰斩·祝福</t>
   </si>
   <si>
     <t>10014</t>
   </si>
   <si>
-    <t>火焰剑法·致命</t>
+    <t>烈焰斩·致命</t>
   </si>
   <si>
     <t>10015</t>
@@ -650,13 +650,13 @@
     <t>2002</t>
   </si>
   <si>
-    <t>神雷术·祝福</t>
+    <t>落雷术·祝福</t>
   </si>
   <si>
     <t>10018</t>
   </si>
   <si>
-    <t>神雷术·致命</t>
+    <t>落雷术·致命</t>
   </si>
   <si>
     <t>10019</t>
@@ -665,13 +665,13 @@
     <t>2003</t>
   </si>
   <si>
-    <t>火墙·祝福</t>
+    <t>火焰墙·祝福</t>
   </si>
   <si>
     <t>10020</t>
   </si>
   <si>
-    <t>火墙·致命</t>
+    <t>火焰墙·致命</t>
   </si>
   <si>
     <t>10021</t>
@@ -680,13 +680,13 @@
     <t>2004</t>
   </si>
   <si>
-    <t>火焰术·祝福</t>
+    <t>烈焰环·祝福</t>
   </si>
   <si>
     <t>10022</t>
   </si>
   <si>
-    <t>火焰术·致命</t>
+    <t>烈焰环·致命</t>
   </si>
   <si>
     <t>10023</t>
@@ -716,13 +716,13 @@
     <t>2007</t>
   </si>
   <si>
-    <t>冰冻术·祝福</t>
+    <t>冰爆术·祝福</t>
   </si>
   <si>
     <t>10028</t>
   </si>
   <si>
-    <t>冰冻术·致命</t>
+    <t>冰爆术·致命</t>
   </si>
   <si>
     <t>10029</t>
@@ -731,13 +731,13 @@
     <t>3001</t>
   </si>
   <si>
-    <t>治疗道法·祝福</t>
+    <t>疗伤术·祝福</t>
   </si>
   <si>
     <t>10030</t>
   </si>
   <si>
-    <t>治疗道法·强化</t>
+    <t>疗伤术·强化</t>
   </si>
   <si>
     <t>技能提高50%技能系数</t>
@@ -749,13 +749,13 @@
     <t>3002</t>
   </si>
   <si>
-    <t>火符道法·祝福</t>
+    <t>驱魔符·祝福</t>
   </si>
   <si>
     <t>10032</t>
   </si>
   <si>
-    <t>火符道法·致命</t>
+    <t>驱魔符·致命</t>
   </si>
   <si>
     <t>10033</t>
@@ -842,13 +842,13 @@
     <t>增加一个持续4回合100%灼烧效果</t>
   </si>
   <si>
-    <t>治疗道法·回复</t>
+    <t>疗伤术·回复</t>
   </si>
   <si>
     <t>增加一个持续4回合100%回复效果</t>
   </si>
   <si>
-    <t>火符道法·中毒</t>
+    <t>驱魔符·中毒</t>
   </si>
   <si>
     <t>增加一个持续4回合50%中毒效果</t>
@@ -860,7 +860,7 @@
     <t>使目标附加50%的伤害,叠加3层,持续4s</t>
   </si>
   <si>
-    <t>冰冻术·冰封</t>
+    <t>冰爆术·冰封</t>
   </si>
   <si>
     <t>增加2S冰冻时间</t>
@@ -878,28 +878,28 @@
     <t>道力精通·祝福</t>
   </si>
   <si>
-    <t>穿刺剑术·吸血</t>
-  </si>
-  <si>
-    <t>冰冻术·哀霜</t>
+    <t>流光剑法·吸血</t>
+  </si>
+  <si>
+    <t>冰爆术·哀霜</t>
   </si>
   <si>
     <t>使敌人受到的伤害增加30%，持续5秒</t>
   </si>
   <si>
-    <t>火焰剑法·血怒</t>
+    <t>烈焰斩·血怒</t>
   </si>
   <si>
     <t>必定暴击</t>
   </si>
   <si>
-    <t>护体神盾·回复</t>
+    <t>战吼·回复</t>
   </si>
   <si>
     <t>回血比例增加1%</t>
   </si>
   <si>
-    <t>瞬移术·叠浪</t>
+    <t>心灵传送·叠浪</t>
   </si>
   <si>
     <t>魔法伤害加成增加3次叠加层数</t>
@@ -911,16 +911,16 @@
     <t>隐身持续时间增加3秒</t>
   </si>
   <si>
-    <t>开天辟地·强化</t>
+    <t>裂天斩·强化</t>
   </si>
   <si>
     <t>造成的比例伤害,增加3%</t>
   </si>
   <si>
-    <t>火雨术·穿透</t>
-  </si>
-  <si>
-    <t>火雨术无视50%护甲</t>
+    <t>毁灭流星·穿透</t>
+  </si>
+  <si>
+    <t>毁灭流星无视50%护甲</t>
   </si>
   <si>
     <t>召唤月神·复制</t>
@@ -947,31 +947,31 @@
     <t>提高此技能系数50%倍率</t>
   </si>
   <si>
-    <t>穿刺剑术·觉醒</t>
-  </si>
-  <si>
-    <t>圆月弯刀·觉醒</t>
+    <t>流光剑法·觉醒</t>
+  </si>
+  <si>
+    <t>旋风斩·觉醒</t>
   </si>
   <si>
     <t>蛮力撞击·觉醒</t>
   </si>
   <si>
-    <t>武力盾·觉醒</t>
+    <t>武神盾·觉醒</t>
   </si>
   <si>
     <t>武力精通·觉醒</t>
   </si>
   <si>
-    <t>火焰剑法·觉醒</t>
-  </si>
-  <si>
-    <t>护体神盾·觉醒</t>
-  </si>
-  <si>
-    <t>开天辟地·觉醒</t>
-  </si>
-  <si>
-    <t>地刺术·觉醒</t>
+    <t>烈焰斩·觉醒</t>
+  </si>
+  <si>
+    <t>战吼·觉醒</t>
+  </si>
+  <si>
+    <t>裂天斩·觉醒</t>
+  </si>
+  <si>
+    <t>裂地斩·觉醒</t>
   </si>
   <si>
     <t>#</t>
@@ -980,7 +980,7 @@
     <t>战士之魂·觉醒</t>
   </si>
   <si>
-    <t>地刺术·大大大</t>
+    <t>裂地斩·大大大</t>
   </si>
   <si>
     <t>增加一圈攻击范围</t>
@@ -989,13 +989,13 @@
     <t>火球术·觉醒</t>
   </si>
   <si>
-    <t>神雷术·觉醒</t>
-  </si>
-  <si>
-    <t>火墙·觉醒</t>
-  </si>
-  <si>
-    <t>火焰术·觉醒</t>
+    <t>落雷术·觉醒</t>
+  </si>
+  <si>
+    <t>火焰墙·觉醒</t>
+  </si>
+  <si>
+    <t>烈焰环·觉醒</t>
   </si>
   <si>
     <t>法力盾·觉醒</t>
@@ -1004,13 +1004,13 @@
     <t>法术精通·觉醒</t>
   </si>
   <si>
-    <t>冰冻术·觉醒</t>
-  </si>
-  <si>
-    <t>瞬移术·觉醒</t>
-  </si>
-  <si>
-    <t>火雨术·觉醒</t>
+    <t>冰爆术·觉醒</t>
+  </si>
+  <si>
+    <t>心灵传送·觉醒</t>
+  </si>
+  <si>
+    <t>毁灭流星·觉醒</t>
   </si>
   <si>
     <t>分身术·觉醒</t>
@@ -1025,10 +1025,10 @@
     <t>提高15S持续时间</t>
   </si>
   <si>
-    <t>治疗道法·觉醒</t>
-  </si>
-  <si>
-    <t>火符道法·觉醒</t>
+    <t>疗伤术·觉醒</t>
+  </si>
+  <si>
+    <t>驱魔符·觉醒</t>
   </si>
   <si>
     <t>毒咒道法·觉醒</t>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="229">
   <si>
     <t>_ID</t>
   </si>
@@ -743,16 +743,10 @@
     <t>技能提高50%技能系数</t>
   </si>
   <si>
-    <t>10031</t>
-  </si>
-  <si>
     <t>3002</t>
   </si>
   <si>
     <t>驱魔符·祝福</t>
-  </si>
-  <si>
-    <t>10032</t>
   </si>
   <si>
     <t>驱魔符·致命</t>
@@ -4493,20 +4487,20 @@
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:26">
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="1">
+        <v>10031</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>51</v>
@@ -4567,8 +4561,8 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:26">
-      <c r="C37" s="1" t="s">
-        <v>129</v>
+      <c r="C37" s="1">
+        <v>10032</v>
       </c>
       <c r="D37" s="1">
         <v>1</v>
@@ -4577,10 +4571,10 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>57</v>
@@ -4642,19 +4636,19 @@
     </row>
     <row r="38" customHeight="1" spans="3:26">
       <c r="C38" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>51</v>
@@ -4716,7 +4710,7 @@
     </row>
     <row r="39" customHeight="1" spans="3:26">
       <c r="C39" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -4725,10 +4719,10 @@
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>57</v>
@@ -4790,19 +4784,19 @@
     </row>
     <row r="40" customHeight="1" spans="3:26">
       <c r="C40" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>51</v>
@@ -4864,22 +4858,22 @@
     </row>
     <row r="41" customHeight="1" spans="3:26">
       <c r="C41" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>52</v>
@@ -4938,19 +4932,19 @@
     </row>
     <row r="42" customHeight="1" spans="3:26">
       <c r="C42" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>76</v>
@@ -5012,7 +5006,7 @@
     </row>
     <row r="43" customHeight="1" spans="3:26">
       <c r="C43" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
@@ -5021,10 +5015,10 @@
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>78</v>
@@ -5086,7 +5080,7 @@
     </row>
     <row r="44" customHeight="1" spans="3:26">
       <c r="C44" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -5160,7 +5154,7 @@
     </row>
     <row r="45" customHeight="1" spans="3:26">
       <c r="C45" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
@@ -5234,19 +5228,19 @@
     </row>
     <row r="46" customHeight="1" spans="3:26">
       <c r="C46" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="1">
-        <v>1</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>51</v>
@@ -5308,22 +5302,22 @@
     </row>
     <row r="47" customHeight="1" spans="3:26">
       <c r="C47" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="D47" s="1">
-        <v>1</v>
-      </c>
-      <c r="E47" s="1">
-        <v>1</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>52</v>
@@ -5655,10 +5649,10 @@
         <v>1001</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -5726,10 +5720,10 @@
         <v>2001</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -5797,10 +5791,10 @@
         <v>3001</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -5868,10 +5862,10 @@
         <v>3002</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -5939,10 +5933,10 @@
         <v>1001</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -6010,10 +6004,10 @@
         <v>2007</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I11" s="3">
         <v>0</v>
@@ -6081,10 +6075,10 @@
         <v>1006</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
@@ -6152,10 +6146,10 @@
         <v>2006</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I13" s="3">
         <v>0</v>
@@ -6223,10 +6217,10 @@
         <v>3006</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -6294,10 +6288,10 @@
         <v>1002</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -6365,10 +6359,10 @@
         <v>2007</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
@@ -6436,10 +6430,10 @@
         <v>1007</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
@@ -6507,10 +6501,10 @@
         <v>1008</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I18" s="4">
         <v>0</v>
@@ -6578,10 +6572,10 @@
         <v>2008</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -6649,10 +6643,10 @@
         <v>3008</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I20" s="4">
         <v>0</v>
@@ -6720,10 +6714,10 @@
         <v>1009</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
@@ -6791,10 +6785,10 @@
         <v>2009</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I22" s="4">
         <v>0</v>
@@ -6862,10 +6856,10 @@
         <v>3009</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I23" s="4">
         <v>0</v>
@@ -6961,16 +6955,16 @@
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>10</v>
@@ -7006,7 +7000,7 @@
         <v>27</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>32</v>
@@ -7072,10 +7066,10 @@
         <v>1001</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I6" s="1">
         <v>50</v>
@@ -7102,10 +7096,10 @@
         <v>1002</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I7" s="1">
         <v>50</v>
@@ -7132,10 +7126,10 @@
         <v>1003</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I8" s="1">
         <v>50</v>
@@ -7161,10 +7155,10 @@
         <v>1004</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I9" s="1">
         <v>50</v>
@@ -7190,10 +7184,10 @@
         <v>1005</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I10" s="1">
         <v>50</v>
@@ -7219,10 +7213,10 @@
         <v>1006</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I11" s="1">
         <v>50</v>
@@ -7248,10 +7242,10 @@
         <v>1007</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I12" s="1">
         <v>50</v>
@@ -7277,10 +7271,10 @@
         <v>1008</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I13" s="1">
         <v>50</v>
@@ -7306,10 +7300,10 @@
         <v>1009</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I14" s="1">
         <v>50</v>
@@ -7335,10 +7329,10 @@
         <v>1010</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I15" s="1">
         <v>50</v>
@@ -7352,10 +7346,10 @@
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C16" s="1">
         <v>11011</v>
@@ -7370,10 +7364,10 @@
         <v>1011</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I16" s="1">
         <v>50</v>
@@ -7403,10 +7397,10 @@
         <v>1010</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I18" s="1">
         <v>50</v>
@@ -7444,10 +7438,10 @@
         <v>2001</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I22" s="1">
         <v>50</v>
@@ -7473,10 +7467,10 @@
         <v>2002</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I23" s="1">
         <v>50</v>
@@ -7502,10 +7496,10 @@
         <v>2003</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I24" s="1">
         <v>50</v>
@@ -7531,10 +7525,10 @@
         <v>2004</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I25" s="1">
         <v>50</v>
@@ -7560,10 +7554,10 @@
         <v>2005</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I26" s="1">
         <v>50</v>
@@ -7589,10 +7583,10 @@
         <v>2006</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I27" s="1">
         <v>50</v>
@@ -7618,10 +7612,10 @@
         <v>2007</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I28" s="1">
         <v>50</v>
@@ -7647,10 +7641,10 @@
         <v>2008</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I29" s="1">
         <v>50</v>
@@ -7676,10 +7670,10 @@
         <v>2009</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I30" s="1">
         <v>50</v>
@@ -7705,10 +7699,10 @@
         <v>2010</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I31" s="1">
         <v>50</v>
@@ -7722,10 +7716,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C32" s="1">
         <v>12011</v>
@@ -7740,10 +7734,10 @@
         <v>2011</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I32" s="1">
         <v>50</v>
@@ -7769,10 +7763,10 @@
         <v>2010</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I34" s="1">
         <v>50</v>
@@ -7810,10 +7804,10 @@
         <v>3001</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I39" s="1">
         <v>50</v>
@@ -7839,10 +7833,10 @@
         <v>3002</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I40" s="1">
         <v>50</v>
@@ -7868,10 +7862,10 @@
         <v>3003</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I41" s="1">
         <v>50</v>
@@ -7897,10 +7891,10 @@
         <v>3004</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I42" s="1">
         <v>50</v>
@@ -7926,10 +7920,10 @@
         <v>3005</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I43" s="1">
         <v>50</v>
@@ -7955,10 +7949,10 @@
         <v>3006</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I44" s="1">
         <v>50</v>
@@ -7984,10 +7978,10 @@
         <v>3007</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I45" s="1">
         <v>50</v>
@@ -8013,10 +8007,10 @@
         <v>3008</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I46" s="1">
         <v>50</v>
@@ -8042,10 +8036,10 @@
         <v>3009</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I47" s="1">
         <v>50</v>
@@ -8071,10 +8065,10 @@
         <v>3010</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I48" s="1">
         <v>50</v>
@@ -8088,10 +8082,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A49" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C49" s="1">
         <v>13011</v>
@@ -8106,10 +8100,10 @@
         <v>3011</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I49" s="1">
         <v>50</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -938,7 +938,7 @@
     <t>基础剑术·觉醒</t>
   </si>
   <si>
-    <t>提高此技能系数50%倍率</t>
+    <t>提高此技能系数50%系数增幅</t>
   </si>
   <si>
     <t>流光剑法·觉醒</t>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
     <sheet name="手动配置" sheetId="2" r:id="rId2"/>
     <sheet name="金装" sheetId="3" r:id="rId3"/>
+    <sheet name="暗金" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -362,8 +363,63 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+攻击力系数（百分比），额外附加固定伤害值</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="253">
   <si>
     <t>_ID</t>
   </si>
@@ -1050,6 +1106,78 @@
   </si>
   <si>
     <t>道士之魂·觉醒</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>SkillLayer</t>
+  </si>
+  <si>
+    <t>一阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高一阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>二阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高二阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>三阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高三阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>四阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高四阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>五阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高五阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>六阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高六阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>七阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高七阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>八阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高八阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>九阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高九阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>十阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高十阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>十一阶·觉醒</t>
+  </si>
+  <si>
+    <t>提高十一阶全系技能系数50%系数增幅</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1190,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,6 +1209,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1569,16 +1703,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1587,124 +1718,129 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -2266,7 +2402,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="3:26">
+    <row r="6" s="5" customFormat="1" customHeight="1" spans="3:26">
       <c r="C6" s="1" t="s">
         <v>48</v>
       </c>
@@ -2340,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="3:26">
+    <row r="7" s="5" customFormat="1" customHeight="1" spans="3:26">
       <c r="C7" s="1" t="s">
         <v>55</v>
       </c>
@@ -2414,7 +2550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="3:26">
+    <row r="8" s="5" customFormat="1" customHeight="1" spans="3:26">
       <c r="C8" s="1" t="s">
         <v>58</v>
       </c>
@@ -2488,7 +2624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" customHeight="1" spans="3:26">
+    <row r="9" s="5" customFormat="1" customHeight="1" spans="3:26">
       <c r="C9" s="1" t="s">
         <v>61</v>
       </c>
@@ -2614,19 +2750,19 @@
       <c r="S10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="W10" s="3" t="s">
+      <c r="T10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="W10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="X10" s="5" t="s">
         <v>52</v>
       </c>
       <c r="Y10" s="1">
@@ -2688,19 +2824,19 @@
       <c r="S11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="T11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="X11" s="3" t="s">
+      <c r="T11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X11" s="5" t="s">
         <v>54</v>
       </c>
       <c r="Y11" s="1">
@@ -2762,19 +2898,19 @@
       <c r="S12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="W12" s="3" t="s">
+      <c r="T12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="U12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="W12" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="X12" s="3" t="s">
+      <c r="X12" s="5" t="s">
         <v>52</v>
       </c>
       <c r="Y12" s="1">
@@ -2836,19 +2972,19 @@
       <c r="S13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="T13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="X13" s="3" t="s">
+      <c r="T13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="U13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="W13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X13" s="5" t="s">
         <v>54</v>
       </c>
       <c r="Y13" s="1">
@@ -5684,22 +5820,22 @@
       <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="T6" s="3">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5">
         <v>0</v>
       </c>
       <c r="Z6" s="1">
@@ -5755,22 +5891,22 @@
       <c r="S7" s="1">
         <v>0</v>
       </c>
-      <c r="T7" s="3">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0</v>
+      </c>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
+      <c r="X7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5">
         <v>0</v>
       </c>
       <c r="Z7" s="1">
@@ -5826,22 +5962,22 @@
       <c r="S8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5">
         <v>0</v>
       </c>
       <c r="Z8" s="1">
@@ -5897,22 +6033,22 @@
       <c r="S9" s="1">
         <v>0</v>
       </c>
-      <c r="T9" s="3">
-        <v>0</v>
-      </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
-      <c r="W9" s="3">
-        <v>0</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0</v>
+      </c>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
+      <c r="X9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="5">
         <v>0</v>
       </c>
       <c r="Z9" s="1">
@@ -5968,30 +6104,30 @@
       <c r="S10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5">
         <v>0</v>
       </c>
       <c r="Z10" s="1">
         <v>107</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:26">
-      <c r="C11" s="3">
+    <row r="11" s="5" customFormat="1" customHeight="1" spans="3:26">
+      <c r="C11" s="5">
         <v>6</v>
       </c>
       <c r="D11" s="1">
@@ -6000,69 +6136,69 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="6">
         <v>2007</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
         <v>2</v>
       </c>
-      <c r="N11" s="3">
-        <v>0</v>
-      </c>
-      <c r="O11" s="3">
-        <v>0</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0</v>
-      </c>
-      <c r="S11" s="3">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="3">
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
         <v>305</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:26">
-      <c r="C12" s="3">
+    <row r="12" s="5" customFormat="1" customHeight="1" spans="3:26">
+      <c r="C12" s="5">
         <v>7</v>
       </c>
       <c r="D12" s="1">
@@ -6071,69 +6207,69 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="5">
         <v>1006</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5">
         <v>50</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0</v>
-      </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:26">
-      <c r="C13" s="3">
+      <c r="R12" s="5">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="5" customFormat="1" customHeight="1" spans="3:26">
+      <c r="C13" s="5">
         <v>8</v>
       </c>
       <c r="D13" s="1">
@@ -6142,69 +6278,69 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="5">
         <v>2006</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0</v>
-      </c>
-      <c r="O13" s="3">
-        <v>0</v>
-      </c>
-      <c r="P13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="3">
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5">
         <v>50</v>
       </c>
-      <c r="R13" s="3">
-        <v>0</v>
-      </c>
-      <c r="S13" s="3">
-        <v>0</v>
-      </c>
-      <c r="T13" s="3">
-        <v>0</v>
-      </c>
-      <c r="U13" s="3">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:26">
-      <c r="C14" s="3">
+      <c r="R13" s="5">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0</v>
+      </c>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
+      <c r="X13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="5" customFormat="1" customHeight="1" spans="3:26">
+      <c r="C14" s="5">
         <v>9</v>
       </c>
       <c r="D14" s="1">
@@ -6213,69 +6349,69 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="5">
         <v>3006</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5">
         <v>50</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:26">
-      <c r="C15" s="3">
+      <c r="R14" s="5">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
+      <c r="X14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="5" customFormat="1" customHeight="1" spans="3:26">
+      <c r="C15" s="5">
         <v>10</v>
       </c>
       <c r="D15" s="1">
@@ -6284,69 +6420,69 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="5">
         <v>1002</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5">
         <v>20</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="R15" s="5">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>0</v>
+      </c>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
+      <c r="X15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
         <v>101</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:26">
-      <c r="C16" s="3">
+    <row r="16" s="5" customFormat="1" customHeight="1" spans="3:26">
+      <c r="C16" s="5">
         <v>11</v>
       </c>
       <c r="D16" s="1">
@@ -6355,69 +6491,69 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="6">
         <v>2007</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
         <v>5</v>
       </c>
-      <c r="N16" s="3">
-        <v>0</v>
-      </c>
-      <c r="O16" s="3">
-        <v>0</v>
-      </c>
-      <c r="P16" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3">
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5">
         <v>30</v>
       </c>
-      <c r="R16" s="3">
-        <v>0</v>
-      </c>
-      <c r="S16" s="3">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3">
-        <v>0</v>
-      </c>
-      <c r="U16" s="3">
-        <v>0</v>
-      </c>
-      <c r="V16" s="3">
-        <v>0</v>
-      </c>
-      <c r="W16" s="3">
-        <v>0</v>
-      </c>
-      <c r="X16" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="3">
+      <c r="R16" s="5">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5">
+        <v>0</v>
+      </c>
+      <c r="X16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
         <v>17</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:26">
-      <c r="C17" s="3">
+    <row r="17" s="5" customFormat="1" customHeight="1" spans="3:26">
+      <c r="C17" s="5">
         <v>12</v>
       </c>
       <c r="D17" s="1">
@@ -6426,69 +6562,69 @@
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="6">
         <v>1007</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="I17" s="4">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="I17" s="6">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
         <v>500</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" ht="17" customHeight="1" spans="3:26">
-      <c r="C18" s="3">
+    <row r="18" s="5" customFormat="1" ht="17" customHeight="1" spans="3:26">
+      <c r="C18" s="5">
         <v>13</v>
       </c>
       <c r="D18" s="1">
@@ -6497,69 +6633,69 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="6">
         <v>1008</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="I18" s="4">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>1</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="I18" s="6">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>1</v>
+      </c>
+      <c r="R18" s="5">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" ht="17" customHeight="1" spans="3:26">
-      <c r="C19" s="3">
+    <row r="19" s="5" customFormat="1" ht="17" customHeight="1" spans="3:26">
+      <c r="C19" s="5">
         <v>14</v>
       </c>
       <c r="D19" s="1">
@@ -6568,69 +6704,69 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="6">
         <v>2008</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="I19" s="4">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3">
+      <c r="I19" s="6">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
         <v>3</v>
       </c>
-      <c r="O19" s="3">
-        <v>0</v>
-      </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>0</v>
-      </c>
-      <c r="R19" s="3">
-        <v>0</v>
-      </c>
-      <c r="S19" s="3">
-        <v>0</v>
-      </c>
-      <c r="T19" s="3">
-        <v>0</v>
-      </c>
-      <c r="U19" s="3">
-        <v>0</v>
-      </c>
-      <c r="V19" s="3">
-        <v>0</v>
-      </c>
-      <c r="W19" s="3">
-        <v>0</v>
-      </c>
-      <c r="X19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="3">
+      <c r="O19" s="5">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5">
+        <v>0</v>
+      </c>
+      <c r="X19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" ht="17" customHeight="1" spans="3:26">
-      <c r="C20" s="3">
+    <row r="20" s="5" customFormat="1" ht="17" customHeight="1" spans="3:26">
+      <c r="C20" s="5">
         <v>15</v>
       </c>
       <c r="D20" s="1">
@@ -6639,69 +6775,69 @@
       <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="6">
         <v>3008</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I20" s="4">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="I20" s="6">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" ht="17" customHeight="1" spans="3:26">
-      <c r="C21" s="3">
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5">
+        <v>0</v>
+      </c>
+      <c r="X20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="5" customFormat="1" ht="17" customHeight="1" spans="3:26">
+      <c r="C21" s="5">
         <v>16</v>
       </c>
       <c r="D21" s="1">
@@ -6710,69 +6846,69 @@
       <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="6">
         <v>1009</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I21" s="4">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="I21" s="6">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="R21" s="5">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5">
+        <v>0</v>
+      </c>
+      <c r="W21" s="5">
+        <v>0</v>
+      </c>
+      <c r="X21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
         <v>109</v>
       </c>
     </row>
-    <row r="22" s="3" customFormat="1" ht="17" customHeight="1" spans="3:26">
-      <c r="C22" s="3">
+    <row r="22" s="5" customFormat="1" ht="17" customHeight="1" spans="3:26">
+      <c r="C22" s="5">
         <v>17</v>
       </c>
       <c r="D22" s="1">
@@ -6781,69 +6917,69 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="6">
         <v>2009</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I22" s="4">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="I22" s="6">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
         <v>50</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="17" customHeight="1" spans="3:26">
-      <c r="C23" s="3">
+      <c r="T22" s="5">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5">
+        <v>0</v>
+      </c>
+      <c r="X22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="5" customFormat="1" ht="17" customHeight="1" spans="3:26">
+      <c r="C23" s="5">
         <v>18</v>
       </c>
       <c r="D23" s="1">
@@ -6852,64 +6988,64 @@
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="6">
         <v>3009</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="I23" s="4">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="I23" s="6">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5">
         <v>2</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="O23" s="5">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
+      <c r="R23" s="5">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5">
+        <v>0</v>
+      </c>
+      <c r="T23" s="5">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0</v>
+      </c>
+      <c r="V23" s="5">
+        <v>0</v>
+      </c>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7080,7 +7216,7 @@
       <c r="K6" s="1">
         <v>0</v>
       </c>
-      <c r="O6" s="3"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="1">
@@ -7110,7 +7246,7 @@
       <c r="K7" s="1">
         <v>0</v>
       </c>
-      <c r="O7" s="3"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
@@ -7154,7 +7290,7 @@
       <c r="F9" s="1">
         <v>1004</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="5" t="s">
         <v>194</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -7224,7 +7360,7 @@
       <c r="J11" s="1">
         <v>0</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7253,7 +7389,7 @@
       <c r="J12" s="1">
         <v>0</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7282,7 +7418,7 @@
       <c r="J13" s="1">
         <v>0</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7311,7 +7447,7 @@
       <c r="J14" s="1">
         <v>0</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7340,7 +7476,7 @@
       <c r="J15" s="1">
         <v>0</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7375,13 +7511,13 @@
       <c r="J16" s="1">
         <v>0</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="10:11">
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C18" s="1">
@@ -7405,24 +7541,24 @@
       <c r="I18" s="1">
         <v>50</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="10:11">
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="10:11">
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="10:11">
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C22" s="1">
@@ -7437,7 +7573,7 @@
       <c r="F22" s="1">
         <v>2001</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="5" t="s">
         <v>205</v>
       </c>
       <c r="H22" s="1" t="s">
@@ -7446,10 +7582,10 @@
       <c r="I22" s="1">
         <v>50</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7475,10 +7611,10 @@
       <c r="I23" s="1">
         <v>50</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7504,10 +7640,10 @@
       <c r="I24" s="1">
         <v>50</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7533,10 +7669,10 @@
       <c r="I25" s="1">
         <v>50</v>
       </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
+      <c r="J25" s="5">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7562,10 +7698,10 @@
       <c r="I26" s="1">
         <v>50</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="J26" s="5">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7582,7 +7718,7 @@
       <c r="F27" s="1">
         <v>2006</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>210</v>
       </c>
       <c r="H27" s="1" t="s">
@@ -7591,10 +7727,10 @@
       <c r="I27" s="1">
         <v>50</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="J27" s="5">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7620,10 +7756,10 @@
       <c r="I28" s="1">
         <v>50</v>
       </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
+      <c r="J28" s="5">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7649,10 +7785,10 @@
       <c r="I29" s="1">
         <v>50</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
+      <c r="J29" s="5">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7678,10 +7814,10 @@
       <c r="I30" s="1">
         <v>50</v>
       </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
+      <c r="J30" s="5">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7707,10 +7843,10 @@
       <c r="I31" s="1">
         <v>50</v>
       </c>
-      <c r="J31" s="3">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3">
+      <c r="J31" s="5">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7742,10 +7878,10 @@
       <c r="I32" s="1">
         <v>50</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="J32" s="5">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7774,21 +7910,21 @@
       <c r="J34" s="1">
         <v>15</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="11:11">
-      <c r="K35" s="3"/>
+      <c r="K35" s="5"/>
     </row>
     <row r="36" customHeight="1" spans="11:11">
-      <c r="K36" s="3"/>
+      <c r="K36" s="5"/>
     </row>
     <row r="37" customHeight="1" spans="11:11">
-      <c r="K37" s="3"/>
+      <c r="K37" s="5"/>
     </row>
     <row r="38" customHeight="1" spans="11:11">
-      <c r="K38" s="3"/>
+      <c r="K38" s="5"/>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C39" s="1">
@@ -7812,10 +7948,10 @@
       <c r="I39" s="1">
         <v>50</v>
       </c>
-      <c r="J39" s="3">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3">
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7832,7 +7968,7 @@
       <c r="F40" s="1">
         <v>3002</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="5" t="s">
         <v>219</v>
       </c>
       <c r="H40" s="1" t="s">
@@ -7841,10 +7977,10 @@
       <c r="I40" s="1">
         <v>50</v>
       </c>
-      <c r="J40" s="3">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3">
+      <c r="J40" s="5">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7870,10 +8006,10 @@
       <c r="I41" s="1">
         <v>50</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="J41" s="5">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7899,10 +8035,10 @@
       <c r="I42" s="1">
         <v>50</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="J42" s="5">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7928,10 +8064,10 @@
       <c r="I43" s="1">
         <v>50</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="J43" s="5">
+        <v>0</v>
+      </c>
+      <c r="K43" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7948,7 +8084,7 @@
       <c r="F44" s="1">
         <v>3006</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="5" t="s">
         <v>223</v>
       </c>
       <c r="H44" s="1" t="s">
@@ -7957,10 +8093,10 @@
       <c r="I44" s="1">
         <v>50</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="J44" s="5">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7986,10 +8122,10 @@
       <c r="I45" s="1">
         <v>50</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="J45" s="5">
+        <v>0</v>
+      </c>
+      <c r="K45" s="5">
         <v>0</v>
       </c>
     </row>
@@ -8015,10 +8151,10 @@
       <c r="I46" s="1">
         <v>50</v>
       </c>
-      <c r="J46" s="3">
-        <v>0</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="J46" s="5">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5">
         <v>0</v>
       </c>
     </row>
@@ -8044,10 +8180,10 @@
       <c r="I47" s="1">
         <v>50</v>
       </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="J47" s="5">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5">
         <v>0</v>
       </c>
     </row>
@@ -8073,10 +8209,10 @@
       <c r="I48" s="1">
         <v>50</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="J48" s="5">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5">
         <v>0</v>
       </c>
     </row>
@@ -8108,10 +8244,10 @@
       <c r="I49" s="1">
         <v>50</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="J49" s="5">
+        <v>0</v>
+      </c>
+      <c r="K49" s="5">
         <v>0</v>
       </c>
     </row>
@@ -8125,4 +8261,472 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:T16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="15.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.25" style="1" customWidth="1"/>
+    <col min="12" max="13" width="7.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.625" style="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.375" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C6" s="1">
+        <v>21001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>200</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C7" s="1">
+        <v>21002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>200</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C8" s="1">
+        <v>21003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>100</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C9" s="1">
+        <v>21004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>100</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C10" s="1">
+        <v>21005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C11" s="1">
+        <v>21006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>100</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C12" s="1">
+        <v>21007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>50</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>7</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="K12" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C13" s="1">
+        <v>21008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>8</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="K13" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C14" s="1">
+        <v>21009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>50</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>9</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="K14" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C15" s="1">
+        <v>21010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K15" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C16" s="1">
+        <v>21011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>11</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="K16" s="1">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -1362,12 +1362,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8409,7 +8409,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -8439,7 +8439,7 @@
         <v>200</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -8469,7 +8469,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -8498,7 +8498,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -8527,7 +8527,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -8556,7 +8556,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -8585,7 +8585,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -8614,7 +8614,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -8643,7 +8643,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -8672,7 +8672,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -8701,7 +8701,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -1114,67 +1114,67 @@
     <t>SkillLayer</t>
   </si>
   <si>
-    <t>一阶·觉醒</t>
+    <t>一阶·掌握</t>
   </si>
   <si>
     <t>提高一阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>二阶·觉醒</t>
+    <t>二阶·掌握</t>
   </si>
   <si>
     <t>提高二阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>三阶·觉醒</t>
+    <t>三阶·掌握</t>
   </si>
   <si>
     <t>提高三阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>四阶·觉醒</t>
+    <t>四阶·掌握</t>
   </si>
   <si>
     <t>提高四阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>五阶·觉醒</t>
+    <t>五阶·掌握</t>
   </si>
   <si>
     <t>提高五阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>六阶·觉醒</t>
+    <t>六阶·掌握</t>
   </si>
   <si>
     <t>提高六阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>七阶·觉醒</t>
+    <t>七阶·掌握</t>
   </si>
   <si>
     <t>提高七阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>八阶·觉醒</t>
+    <t>八阶·掌握</t>
   </si>
   <si>
     <t>提高八阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>九阶·觉醒</t>
+    <t>九阶·掌握</t>
   </si>
   <si>
     <t>提高九阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>十阶·觉醒</t>
+    <t>十阶·掌握</t>
   </si>
   <si>
     <t>提高十阶全系技能系数50%系数增幅</t>
   </si>
   <si>
-    <t>十一阶·觉醒</t>
+    <t>十一阶·掌握</t>
   </si>
   <si>
     <t>提高十一阶全系技能系数50%系数增幅</t>
@@ -1362,12 +1362,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -8406,7 +8406,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -8698,7 +8698,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -419,7 +419,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="249">
   <si>
     <t>_ID</t>
   </si>
@@ -1024,12 +1024,6 @@
     <t>裂地斩·觉醒</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>战士之魂·觉醒</t>
-  </si>
-  <si>
     <t>裂地斩·大大大</t>
   </si>
   <si>
@@ -1066,9 +1060,6 @@
     <t>分身术·觉醒</t>
   </si>
   <si>
-    <t>法师之魂·觉醒</t>
-  </si>
-  <si>
     <t>分身术·持久</t>
   </si>
   <si>
@@ -1103,9 +1094,6 @@
   </si>
   <si>
     <t>无极道体·觉醒</t>
-  </si>
-  <si>
-    <t>道士之魂·觉醒</t>
   </si>
   <si>
     <t>Role</t>
@@ -7064,7 +7052,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:R49"/>
+  <dimension ref="C3:R44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -7459,7 +7447,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F15" s="1">
         <v>1010</v>
@@ -7480,100 +7468,119 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A16" s="1" t="s">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C16" s="1">
+        <v>11110</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1010</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" s="1">
-        <v>11011</v>
-      </c>
-      <c r="D16" s="1">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1011</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="I16" s="1">
         <v>50</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="5">
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="10:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="10:11">
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C18" s="1">
-        <v>11110</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1">
-        <v>5</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1010</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="I18" s="1">
-        <v>50</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5">
-        <v>1</v>
-      </c>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="10:11">
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="10:11">
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="10:11">
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="10:11">
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C20" s="1">
+        <v>12001</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>200</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2001</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I20" s="1">
+        <v>50</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C21" s="1">
+        <v>12002</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>200</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I21" s="1">
+        <v>50</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C22" s="1">
-        <v>12001</v>
+        <v>12003</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F22" s="1">
-        <v>2001</v>
-      </c>
-      <c r="G22" s="5" t="s">
+        <v>2003</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>205</v>
       </c>
       <c r="H22" s="1" t="s">
@@ -7591,16 +7598,16 @@
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C23" s="1">
-        <v>12002</v>
+        <v>12004</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
       </c>
       <c r="E23" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F23" s="1">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>206</v>
@@ -7620,7 +7627,7 @@
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C24" s="1">
-        <v>12003</v>
+        <v>12005</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
@@ -7629,7 +7636,7 @@
         <v>100</v>
       </c>
       <c r="F24" s="1">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>207</v>
@@ -7649,7 +7656,7 @@
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C25" s="1">
-        <v>12004</v>
+        <v>12006</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
@@ -7658,9 +7665,9 @@
         <v>100</v>
       </c>
       <c r="F25" s="1">
-        <v>2004</v>
-      </c>
-      <c r="G25" s="1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>208</v>
       </c>
       <c r="H25" s="1" t="s">
@@ -7678,16 +7685,16 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C26" s="1">
-        <v>12005</v>
+        <v>12007</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
       </c>
       <c r="E26" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F26" s="1">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>209</v>
@@ -7707,18 +7714,18 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C27" s="1">
-        <v>12006</v>
+        <v>12008</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F27" s="1">
-        <v>2006</v>
-      </c>
-      <c r="G27" s="5" t="s">
+        <v>2008</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>210</v>
       </c>
       <c r="H27" s="1" t="s">
@@ -7736,7 +7743,7 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C28" s="1">
-        <v>12007</v>
+        <v>12009</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -7745,7 +7752,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="1">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>211</v>
@@ -7765,16 +7772,16 @@
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C29" s="1">
-        <v>12008</v>
+        <v>12010</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
       <c r="E29" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F29" s="1">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>212</v>
@@ -7794,153 +7801,176 @@
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C30" s="1">
-        <v>12009</v>
+        <v>12110</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
       </c>
       <c r="E30" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F30" s="1">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>213</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="I30" s="1">
         <v>50</v>
       </c>
-      <c r="J30" s="5">
-        <v>0</v>
+      <c r="J30" s="1">
+        <v>15</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C31" s="1">
-        <v>12010</v>
-      </c>
-      <c r="D31" s="1">
+    <row r="31" customHeight="1" spans="11:11">
+      <c r="K31" s="5"/>
+    </row>
+    <row r="32" customHeight="1" spans="11:11">
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" customHeight="1" spans="11:11">
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" customHeight="1" spans="11:11">
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C35" s="1">
+        <v>13001</v>
+      </c>
+      <c r="D35" s="1">
         <v>2</v>
       </c>
-      <c r="E31" s="1">
-        <v>5</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2010</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="E35" s="1">
+        <v>200</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3001</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I35" s="1">
         <v>50</v>
       </c>
-      <c r="J31" s="5">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C32" s="1">
-        <v>12011</v>
-      </c>
-      <c r="D32" s="1">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2011</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="J35" s="5">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C36" s="1">
+        <v>13002</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>200</v>
+      </c>
+      <c r="F36" s="1">
+        <v>3002</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I36" s="1">
         <v>50</v>
       </c>
-      <c r="J32" s="5">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C34" s="1">
-        <v>12110</v>
-      </c>
-      <c r="D34" s="1">
-        <v>3</v>
-      </c>
-      <c r="E34" s="1">
-        <v>5</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2010</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="J36" s="5">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C37" s="1">
+        <v>13003</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>100</v>
+      </c>
+      <c r="F37" s="1">
+        <v>3003</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I34" s="1">
+      <c r="H37" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I37" s="1">
         <v>50</v>
       </c>
-      <c r="J34" s="1">
-        <v>15</v>
-      </c>
-      <c r="K34" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="11:11">
-      <c r="K35" s="5"/>
-    </row>
-    <row r="36" customHeight="1" spans="11:11">
-      <c r="K36" s="5"/>
-    </row>
-    <row r="37" customHeight="1" spans="11:11">
-      <c r="K37" s="5"/>
-    </row>
-    <row r="38" customHeight="1" spans="11:11">
-      <c r="K38" s="5"/>
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C38" s="1">
+        <v>13004</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>100</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3004</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I38" s="1">
+        <v>50</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C39" s="1">
-        <v>13001</v>
+        <v>13005</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
       <c r="E39" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F39" s="1">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>191</v>
@@ -7957,19 +7987,19 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C40" s="1">
-        <v>13002</v>
+        <v>13006</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F40" s="1">
-        <v>3002</v>
+        <v>3006</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>191</v>
@@ -7986,19 +8016,19 @@
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C41" s="1">
-        <v>13003</v>
+        <v>13007</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F41" s="1">
-        <v>3003</v>
+        <v>3007</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>191</v>
@@ -8015,19 +8045,19 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C42" s="1">
-        <v>13004</v>
+        <v>13008</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
       <c r="E42" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F42" s="1">
-        <v>3004</v>
+        <v>3008</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>191</v>
@@ -8044,19 +8074,19 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C43" s="1">
-        <v>13005</v>
+        <v>13009</v>
       </c>
       <c r="D43" s="1">
         <v>2</v>
       </c>
       <c r="E43" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F43" s="1">
-        <v>3005</v>
+        <v>3009</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>191</v>
@@ -8073,19 +8103,19 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C44" s="1">
-        <v>13006</v>
+        <v>13010</v>
       </c>
       <c r="D44" s="1">
         <v>2</v>
       </c>
       <c r="E44" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F44" s="1">
-        <v>3006</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>223</v>
+        <v>3010</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>191</v>
@@ -8097,157 +8127,6 @@
         <v>0</v>
       </c>
       <c r="K44" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C45" s="1">
-        <v>13007</v>
-      </c>
-      <c r="D45" s="1">
-        <v>2</v>
-      </c>
-      <c r="E45" s="1">
-        <v>50</v>
-      </c>
-      <c r="F45" s="1">
-        <v>3007</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I45" s="1">
-        <v>50</v>
-      </c>
-      <c r="J45" s="5">
-        <v>0</v>
-      </c>
-      <c r="K45" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C46" s="1">
-        <v>13008</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="1">
-        <v>50</v>
-      </c>
-      <c r="F46" s="1">
-        <v>3008</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I46" s="1">
-        <v>50</v>
-      </c>
-      <c r="J46" s="5">
-        <v>0</v>
-      </c>
-      <c r="K46" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C47" s="1">
-        <v>13009</v>
-      </c>
-      <c r="D47" s="1">
-        <v>2</v>
-      </c>
-      <c r="E47" s="1">
-        <v>50</v>
-      </c>
-      <c r="F47" s="1">
-        <v>3009</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I47" s="1">
-        <v>50</v>
-      </c>
-      <c r="J47" s="5">
-        <v>0</v>
-      </c>
-      <c r="K47" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C48" s="1">
-        <v>13010</v>
-      </c>
-      <c r="D48" s="1">
-        <v>2</v>
-      </c>
-      <c r="E48" s="1">
-        <v>5</v>
-      </c>
-      <c r="F48" s="1">
-        <v>3010</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I48" s="1">
-        <v>50</v>
-      </c>
-      <c r="J48" s="5">
-        <v>0</v>
-      </c>
-      <c r="K48" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A49" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C49" s="1">
-        <v>13011</v>
-      </c>
-      <c r="D49" s="1">
-        <v>3</v>
-      </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="1">
-        <v>3011</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I49" s="1">
-        <v>50</v>
-      </c>
-      <c r="J49" s="5">
-        <v>0</v>
-      </c>
-      <c r="K49" s="5">
         <v>0</v>
       </c>
     </row>
@@ -8295,13 +8174,13 @@
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>186</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>4</v>
@@ -8333,13 +8212,13 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>26</v>
@@ -8418,10 +8297,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K6" s="1">
         <v>50</v>
@@ -8448,10 +8327,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K7" s="1">
         <v>50</v>
@@ -8478,10 +8357,10 @@
         <v>3</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K8" s="1">
         <v>50</v>
@@ -8507,10 +8386,10 @@
         <v>4</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K9" s="1">
         <v>50</v>
@@ -8536,10 +8415,10 @@
         <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K10" s="1">
         <v>50</v>
@@ -8565,10 +8444,10 @@
         <v>6</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K11" s="1">
         <v>50</v>
@@ -8594,10 +8473,10 @@
         <v>7</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K12" s="1">
         <v>50</v>
@@ -8623,10 +8502,10 @@
         <v>8</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="K13" s="1">
         <v>50</v>
@@ -8652,10 +8531,10 @@
         <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K14" s="1">
         <v>50</v>
@@ -8681,10 +8560,10 @@
         <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="K15" s="1">
         <v>50</v>
@@ -8710,10 +8589,10 @@
         <v>11</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K16" s="1">
         <v>50</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowWidth="27952" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -2154,17 +2154,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="21.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.2477876106195" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.8761061946903" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="14.625" style="1" customWidth="1"/>
-    <col min="11" max="13" width="10.375" style="1" customWidth="1"/>
-    <col min="14" max="16" width="13.75" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6283185840708" style="1" customWidth="1"/>
+    <col min="11" max="13" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="14" max="16" width="13.7522123893805" style="1" customWidth="1"/>
+    <col min="17" max="17" width="10.3716814159292" style="1" customWidth="1"/>
     <col min="18" max="25" width="13" style="1" customWidth="1"/>
-    <col min="26" max="26" width="7.875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.87610619469027" style="1" customWidth="1"/>
     <col min="27" max="32" width="9" style="1"/>
-    <col min="33" max="33" width="19.25" style="1" customWidth="1"/>
+    <col min="33" max="33" width="19.2477876106195" style="1" customWidth="1"/>
     <col min="34" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5518,22 +5518,22 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="13.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7522123893805" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.1238938053097" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
-    <col min="10" max="13" width="10.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.875" style="1" customWidth="1"/>
-    <col min="15" max="16" width="13.75" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.375" style="1" customWidth="1"/>
+    <col min="10" max="13" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.8761061946903" style="1" customWidth="1"/>
+    <col min="15" max="16" width="13.7522123893805" style="1" customWidth="1"/>
+    <col min="17" max="17" width="10.3716814159292" style="1" customWidth="1"/>
     <col min="18" max="19" width="13" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.5" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.50442477876106" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.6283185840708" style="1" customWidth="1"/>
+    <col min="22" max="22" width="12.6283185840708" style="1" customWidth="1"/>
     <col min="23" max="23" width="9" style="1" customWidth="1"/>
-    <col min="24" max="25" width="9.75" style="1" customWidth="1"/>
-    <col min="26" max="26" width="7.875" style="1" customWidth="1"/>
+    <col min="24" max="25" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.87610619469027" style="1" customWidth="1"/>
     <col min="27" max="32" width="9" style="1"/>
-    <col min="33" max="33" width="19.25" style="1" customWidth="1"/>
+    <col min="33" max="33" width="19.2477876106195" style="1" customWidth="1"/>
     <col min="34" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7056,15 +7056,15 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="15.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.25" style="1" customWidth="1"/>
-    <col min="10" max="11" width="10.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6283185840708" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.1238938053097" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.2477876106195" style="1" customWidth="1"/>
+    <col min="10" max="11" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.50442477876106" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.6283185840708" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6283185840708" style="1" customWidth="1"/>
     <col min="15" max="17" width="13" style="1" customWidth="1"/>
-    <col min="18" max="18" width="7.375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="7.3716814159292" style="1" customWidth="1"/>
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7476,7 +7476,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1">
         <v>1010</v>
@@ -7807,7 +7807,7 @@
         <v>2</v>
       </c>
       <c r="E30" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F30" s="1">
         <v>2010</v>
@@ -8149,17 +8149,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.8761061946903" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="15.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="25.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.25" style="1" customWidth="1"/>
-    <col min="12" max="13" width="7.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6283185840708" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.6283185840708" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.2477876106195" style="1" customWidth="1"/>
+    <col min="12" max="13" width="7.75221238938053" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.50442477876106" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6283185840708" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6283185840708" style="1" customWidth="1"/>
     <col min="17" max="19" width="13" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.3716814159292" style="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -9422,7 +9422,7 @@
         <v>31001</v>
       </c>
       <c r="D6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1">
         <v>300</v>
@@ -9461,7 +9461,7 @@
         <v>31002</v>
       </c>
       <c r="D7" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -9500,7 +9500,7 @@
         <v>31003</v>
       </c>
       <c r="D8" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
         <v>300</v>
@@ -9538,7 +9538,7 @@
         <v>31004</v>
       </c>
       <c r="D9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1">
         <v>300</v>
@@ -9576,7 +9576,7 @@
         <v>31005</v>
       </c>
       <c r="D10" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1">
         <v>100</v>
@@ -9614,7 +9614,7 @@
         <v>31006</v>
       </c>
       <c r="D11" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -9652,7 +9652,7 @@
         <v>31007</v>
       </c>
       <c r="D12" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1">
         <v>300</v>
@@ -9690,7 +9690,7 @@
         <v>31008</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
@@ -9728,7 +9728,7 @@
         <v>31009</v>
       </c>
       <c r="D14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1">
         <v>300</v>
@@ -9766,7 +9766,7 @@
         <v>31010</v>
       </c>
       <c r="D15" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -9804,7 +9804,7 @@
         <v>31011</v>
       </c>
       <c r="D16" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1">
         <v>10</v>
@@ -9842,7 +9842,7 @@
         <v>31012</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1">
         <v>10</v>
@@ -9877,7 +9877,7 @@
         <v>31112</v>
       </c>
       <c r="D18" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="1">
         <v>10</v>
@@ -9918,7 +9918,7 @@
         <v>31212</v>
       </c>
       <c r="D19" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="1">
         <v>10</v>
@@ -9956,7 +9956,7 @@
         <v>31312</v>
       </c>
       <c r="D20" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="1">
         <v>10</v>
@@ -10010,7 +10010,7 @@
         <v>32001</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="1">
         <v>300</v>
@@ -10045,7 +10045,7 @@
         <v>32002</v>
       </c>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
@@ -10080,7 +10080,7 @@
         <v>32003</v>
       </c>
       <c r="D27" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="1">
         <v>300</v>
@@ -10115,7 +10115,7 @@
         <v>32004</v>
       </c>
       <c r="D28" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="1">
         <v>300</v>
@@ -10150,7 +10150,7 @@
         <v>32005</v>
       </c>
       <c r="D29" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" s="1">
         <v>100</v>
@@ -10185,7 +10185,7 @@
         <v>32006</v>
       </c>
       <c r="D30" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="1">
         <v>50</v>
@@ -10220,7 +10220,7 @@
         <v>32007</v>
       </c>
       <c r="D31" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="1">
         <v>300</v>
@@ -10255,7 +10255,7 @@
         <v>32008</v>
       </c>
       <c r="D32" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" s="1">
         <v>50</v>
@@ -10290,7 +10290,7 @@
         <v>32009</v>
       </c>
       <c r="D33" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" s="1">
         <v>300</v>
@@ -10325,7 +10325,7 @@
         <v>32010</v>
       </c>
       <c r="D34" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="1">
         <v>10</v>
@@ -10360,7 +10360,7 @@
         <v>32011</v>
       </c>
       <c r="D35" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="1">
         <v>10</v>
@@ -10395,7 +10395,7 @@
         <v>32012</v>
       </c>
       <c r="D36" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="1">
         <v>10</v>
@@ -10438,7 +10438,7 @@
         <v>32102</v>
       </c>
       <c r="D39" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="1">
         <v>10</v>
@@ -10470,10 +10470,10 @@
     </row>
     <row r="40" customHeight="1" spans="3:14">
       <c r="C40" s="1">
-        <v>32102</v>
+        <v>32202</v>
       </c>
       <c r="D40" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" s="1">
         <v>10</v>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="41" customHeight="1" spans="3:14">
       <c r="C41" s="1">
-        <v>32010</v>
+        <v>32110</v>
       </c>
       <c r="D41" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" s="1">
         <v>10</v>
@@ -10540,10 +10540,10 @@
     </row>
     <row r="42" customHeight="1" spans="3:14">
       <c r="C42" s="1">
-        <v>32008</v>
+        <v>32108</v>
       </c>
       <c r="D42" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="1">
         <v>10</v>
@@ -10575,10 +10575,10 @@
     </row>
     <row r="43" customHeight="1" spans="3:14">
       <c r="C43" s="1">
-        <v>32007</v>
+        <v>32107</v>
       </c>
       <c r="D43" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="1">
         <v>10</v>
@@ -10610,10 +10610,10 @@
     </row>
     <row r="44" customHeight="1" spans="3:14">
       <c r="C44" s="1">
-        <v>32012</v>
+        <v>32112</v>
       </c>
       <c r="D44" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" s="1">
         <v>10</v>
@@ -10653,7 +10653,7 @@
         <v>33001</v>
       </c>
       <c r="D46" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" s="1">
         <v>300</v>
@@ -10688,7 +10688,7 @@
         <v>33002</v>
       </c>
       <c r="D47" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" s="1">
         <v>50</v>
@@ -10723,7 +10723,7 @@
         <v>33003</v>
       </c>
       <c r="D48" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" s="1">
         <v>300</v>
@@ -10758,7 +10758,7 @@
         <v>33004</v>
       </c>
       <c r="D49" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" s="1">
         <v>300</v>
@@ -10793,7 +10793,7 @@
         <v>33005</v>
       </c>
       <c r="D50" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" s="1">
         <v>100</v>
@@ -10828,7 +10828,7 @@
         <v>33006</v>
       </c>
       <c r="D51" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51" s="1">
         <v>50</v>
@@ -10863,7 +10863,7 @@
         <v>33007</v>
       </c>
       <c r="D52" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52" s="1">
         <v>300</v>
@@ -10898,7 +10898,7 @@
         <v>33008</v>
       </c>
       <c r="D53" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53" s="1">
         <v>50</v>
@@ -10933,7 +10933,7 @@
         <v>33009</v>
       </c>
       <c r="D54" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" s="1">
         <v>300</v>
@@ -10968,7 +10968,7 @@
         <v>33010</v>
       </c>
       <c r="D55" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" s="1">
         <v>10</v>
@@ -11003,7 +11003,7 @@
         <v>33011</v>
       </c>
       <c r="D56" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E56" s="1">
         <v>10</v>
@@ -11038,7 +11038,7 @@
         <v>33012</v>
       </c>
       <c r="D57" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" s="1">
         <v>10</v>
@@ -11088,7 +11088,7 @@
         <v>33112</v>
       </c>
       <c r="D59" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" s="1">
         <v>10</v>
@@ -11126,10 +11126,10 @@
     </row>
     <row r="60" customHeight="1" spans="3:14">
       <c r="C60" s="1">
-        <v>33008</v>
+        <v>33108</v>
       </c>
       <c r="D60" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" s="1">
         <v>10</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -470,12 +470,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="P3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+攻击力系数（百分比），额外附加固定伤害值</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="310">
   <si>
     <t>_ID</t>
   </si>
@@ -1228,6 +1250,18 @@
   </si>
   <si>
     <t>提高十一阶全系技能系数50%系数增幅</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Miss</t>
   </si>
   <si>
     <t>基础剑术·通神</t>
@@ -1577,12 +1611,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2377,7 +2411,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AA47"/>
+  <dimension ref="C3:AC47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="7" width="9" style="1"/>
@@ -2395,7 +2429,7 @@
     <col min="35" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:27">
+    <row r="3" customHeight="1" spans="3:29">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2471,8 +2505,10 @@
       <c r="AA3" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:27">
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+    </row>
+    <row r="4" customHeight="1" spans="3:29">
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
@@ -2548,8 +2584,10 @@
       <c r="AA4" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:27">
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+    </row>
+    <row r="5" customHeight="1" spans="3:29">
       <c r="C5" s="2" t="s">
         <v>47</v>
       </c>
@@ -2625,6 +2663,8 @@
       <c r="AA5" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="3:27">
       <c r="C6" s="1" t="s">
@@ -5862,7 +5902,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 C5:D5 E5 F5 G3:J5 C3:D4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:J5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -7541,7 +7581,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 G3:J5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:J5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -8739,7 +8779,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 G3:I5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -9249,7 +9289,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 G3:K5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -9273,7 +9313,7 @@
     <col min="12" max="12" width="13.25" style="1" customWidth="1"/>
     <col min="13" max="14" width="13" style="1" customWidth="1"/>
     <col min="15" max="15" width="7.75" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.375" style="1" customWidth="1"/>
     <col min="17" max="19" width="13" style="1" customWidth="1"/>
     <col min="20" max="20" width="7.375" style="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="1"/>
@@ -9319,9 +9359,15 @@
       <c r="O3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
     </row>
@@ -9365,9 +9411,15 @@
       <c r="O4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
+      <c r="P4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
     </row>
@@ -9411,13 +9463,19 @@
       <c r="O5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
+      <c r="P5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>31001</v>
       </c>
@@ -9440,7 +9498,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>193</v>
@@ -9454,9 +9512,17 @@
       <c r="N6" s="1">
         <v>0</v>
       </c>
-      <c r="Q6" s="4"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>31002</v>
       </c>
@@ -9479,7 +9545,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>193</v>
@@ -9493,9 +9559,17 @@
       <c r="N7" s="1">
         <v>0</v>
       </c>
-      <c r="Q7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>31003</v>
       </c>
@@ -9518,7 +9592,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>193</v>
@@ -9532,8 +9606,17 @@
       <c r="N8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>31004</v>
       </c>
@@ -9556,7 +9639,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>193</v>
@@ -9570,8 +9653,17 @@
       <c r="N9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>31005</v>
       </c>
@@ -9594,7 +9686,7 @@
         <v>5</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>193</v>
@@ -9608,8 +9700,17 @@
       <c r="N10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>31006</v>
       </c>
@@ -9632,7 +9733,7 @@
         <v>6</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>193</v>
@@ -9646,8 +9747,17 @@
       <c r="N11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C12" s="1">
         <v>31007</v>
       </c>
@@ -9670,7 +9780,7 @@
         <v>7</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>193</v>
@@ -9684,8 +9794,17 @@
       <c r="N12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C13" s="1">
         <v>31008</v>
       </c>
@@ -9708,7 +9827,7 @@
         <v>8</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>193</v>
@@ -9722,8 +9841,17 @@
       <c r="N13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C14" s="1">
         <v>31009</v>
       </c>
@@ -9746,7 +9874,7 @@
         <v>9</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>193</v>
@@ -9760,8 +9888,17 @@
       <c r="N14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C15" s="1">
         <v>31010</v>
       </c>
@@ -9784,7 +9921,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>193</v>
@@ -9798,8 +9935,17 @@
       <c r="N15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C16" s="1">
         <v>31011</v>
       </c>
@@ -9822,7 +9968,7 @@
         <v>11</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>193</v>
@@ -9836,8 +9982,17 @@
       <c r="N16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:14">
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:18">
       <c r="C17" s="1">
         <v>31012</v>
       </c>
@@ -9857,7 +10012,7 @@
         <v>1012</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>193</v>
@@ -9871,8 +10026,17 @@
       <c r="N17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C18" s="1">
         <v>31112</v>
       </c>
@@ -9895,10 +10059,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -9912,8 +10076,17 @@
       <c r="O18" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P18" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C19" s="1">
         <v>31212</v>
       </c>
@@ -9936,10 +10109,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -9950,8 +10123,17 @@
       <c r="N19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C20" s="1">
         <v>31312</v>
       </c>
@@ -9974,10 +10156,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -9988,24 +10170,37 @@
       <c r="N20" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="8:10">
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="8:16">
       <c r="H21" s="3"/>
       <c r="J21" s="3"/>
-    </row>
-    <row r="22" customHeight="1" spans="8:10">
+      <c r="P21" s="4"/>
+    </row>
+    <row r="22" customHeight="1" spans="8:16">
       <c r="H22" s="3"/>
       <c r="J22" s="3"/>
-    </row>
-    <row r="23" customHeight="1" spans="8:10">
+      <c r="P22" s="4"/>
+    </row>
+    <row r="23" customHeight="1" spans="8:16">
       <c r="H23" s="3"/>
       <c r="J23" s="3"/>
-    </row>
-    <row r="24" customHeight="1" spans="8:10">
+      <c r="P23" s="4"/>
+    </row>
+    <row r="24" customHeight="1" spans="8:16">
       <c r="H24" s="3"/>
       <c r="J24" s="3"/>
-    </row>
-    <row r="25" customHeight="1" spans="3:14">
+      <c r="P24" s="4"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:18">
       <c r="C25" s="1">
         <v>32001</v>
       </c>
@@ -10025,7 +10220,7 @@
         <v>2001</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>193</v>
@@ -10039,8 +10234,17 @@
       <c r="N25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:14">
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:18">
       <c r="C26" s="1">
         <v>32002</v>
       </c>
@@ -10060,7 +10264,7 @@
         <v>2002</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>193</v>
@@ -10074,8 +10278,17 @@
       <c r="N26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:14">
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:18">
       <c r="C27" s="1">
         <v>32003</v>
       </c>
@@ -10095,7 +10308,7 @@
         <v>2003</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>193</v>
@@ -10109,8 +10322,17 @@
       <c r="N27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:14">
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:18">
       <c r="C28" s="1">
         <v>32004</v>
       </c>
@@ -10130,7 +10352,7 @@
         <v>2004</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>193</v>
@@ -10144,8 +10366,17 @@
       <c r="N28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:14">
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:18">
       <c r="C29" s="1">
         <v>32005</v>
       </c>
@@ -10165,7 +10396,7 @@
         <v>2005</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>193</v>
@@ -10179,8 +10410,17 @@
       <c r="N29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:14">
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:18">
       <c r="C30" s="1">
         <v>32006</v>
       </c>
@@ -10200,7 +10440,7 @@
         <v>2006</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
@@ -10214,8 +10454,17 @@
       <c r="N30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:14">
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:18">
       <c r="C31" s="1">
         <v>32007</v>
       </c>
@@ -10235,7 +10484,7 @@
         <v>2007</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>193</v>
@@ -10249,8 +10498,17 @@
       <c r="N31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:14">
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:18">
       <c r="C32" s="1">
         <v>32008</v>
       </c>
@@ -10270,7 +10528,7 @@
         <v>2008</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>193</v>
@@ -10284,8 +10542,17 @@
       <c r="N32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:14">
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>0</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:18">
       <c r="C33" s="1">
         <v>32009</v>
       </c>
@@ -10305,7 +10572,7 @@
         <v>2009</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>193</v>
@@ -10319,8 +10586,17 @@
       <c r="N33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:14">
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:18">
       <c r="C34" s="1">
         <v>32010</v>
       </c>
@@ -10340,7 +10616,7 @@
         <v>2010</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>193</v>
@@ -10354,8 +10630,17 @@
       <c r="N34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:14">
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:18">
       <c r="C35" s="1">
         <v>32011</v>
       </c>
@@ -10375,7 +10660,7 @@
         <v>2011</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>193</v>
@@ -10389,8 +10674,17 @@
       <c r="N35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:14">
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:18">
       <c r="C36" s="1">
         <v>32012</v>
       </c>
@@ -10410,7 +10704,7 @@
         <v>2012</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>193</v>
@@ -10422,6 +10716,15 @@
         <v>0</v>
       </c>
       <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
         <v>0</v>
       </c>
     </row>
@@ -10433,7 +10736,7 @@
       <c r="H38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="3:14">
+    <row r="39" customHeight="1" spans="3:18">
       <c r="C39" s="1">
         <v>32102</v>
       </c>
@@ -10453,10 +10756,10 @@
         <v>2002</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L39" s="1">
         <v>50</v>
@@ -10467,8 +10770,20 @@
       <c r="N39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:14">
+      <c r="O39" s="1">
+        <v>101</v>
+      </c>
+      <c r="P39" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:18">
       <c r="C40" s="1">
         <v>32202</v>
       </c>
@@ -10488,10 +10803,10 @@
         <v>2002</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="L40" s="1">
         <v>50</v>
@@ -10502,8 +10817,17 @@
       <c r="N40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:14">
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:18">
       <c r="C41" s="1">
         <v>32110</v>
       </c>
@@ -10523,10 +10847,10 @@
         <v>2010</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="L41" s="1">
         <v>50</v>
@@ -10537,8 +10861,17 @@
       <c r="N41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:14">
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:18">
       <c r="C42" s="1">
         <v>32108</v>
       </c>
@@ -10558,7 +10891,7 @@
         <v>2008</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>193</v>
@@ -10572,8 +10905,17 @@
       <c r="N42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:14">
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:18">
       <c r="C43" s="1">
         <v>32107</v>
       </c>
@@ -10593,10 +10935,10 @@
         <v>2007</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="L43" s="1">
         <v>50</v>
@@ -10607,8 +10949,17 @@
       <c r="N43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:14">
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:18">
       <c r="C44" s="1">
         <v>32112</v>
       </c>
@@ -10628,10 +10979,10 @@
         <v>2012</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="L44" s="1">
         <v>50</v>
@@ -10640,6 +10991,15 @@
         <v>0</v>
       </c>
       <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
         <v>0</v>
       </c>
     </row>
@@ -10648,7 +11008,7 @@
       <c r="J45" s="3"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="3:14">
+    <row r="46" customHeight="1" spans="3:18">
       <c r="C46" s="1">
         <v>33001</v>
       </c>
@@ -10668,7 +11028,7 @@
         <v>3001</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>193</v>
@@ -10682,8 +11042,17 @@
       <c r="N46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:14">
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:18">
       <c r="C47" s="1">
         <v>33002</v>
       </c>
@@ -10703,7 +11072,7 @@
         <v>3002</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>193</v>
@@ -10717,8 +11086,17 @@
       <c r="N47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:14">
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:18">
       <c r="C48" s="1">
         <v>33003</v>
       </c>
@@ -10738,7 +11116,7 @@
         <v>3003</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>193</v>
@@ -10752,8 +11130,17 @@
       <c r="N48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:14">
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:18">
       <c r="C49" s="1">
         <v>33004</v>
       </c>
@@ -10773,7 +11160,7 @@
         <v>3004</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>193</v>
@@ -10787,8 +11174,17 @@
       <c r="N49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:14">
+      <c r="P49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:18">
       <c r="C50" s="1">
         <v>33005</v>
       </c>
@@ -10808,7 +11204,7 @@
         <v>3005</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>193</v>
@@ -10822,8 +11218,17 @@
       <c r="N50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:14">
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:18">
       <c r="C51" s="1">
         <v>33006</v>
       </c>
@@ -10843,7 +11248,7 @@
         <v>3006</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>193</v>
@@ -10857,8 +11262,17 @@
       <c r="N51" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:14">
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:18">
       <c r="C52" s="1">
         <v>33007</v>
       </c>
@@ -10878,7 +11292,7 @@
         <v>3007</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>193</v>
@@ -10892,8 +11306,17 @@
       <c r="N52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:14">
+      <c r="P52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:18">
       <c r="C53" s="1">
         <v>33008</v>
       </c>
@@ -10913,7 +11336,7 @@
         <v>3008</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>193</v>
@@ -10927,8 +11350,17 @@
       <c r="N53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:14">
+      <c r="P53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:18">
       <c r="C54" s="1">
         <v>33009</v>
       </c>
@@ -10948,7 +11380,7 @@
         <v>3009</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>193</v>
@@ -10962,8 +11394,17 @@
       <c r="N54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:14">
+      <c r="P54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:18">
       <c r="C55" s="1">
         <v>33010</v>
       </c>
@@ -10983,7 +11424,7 @@
         <v>3010</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>193</v>
@@ -10997,8 +11438,17 @@
       <c r="N55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:14">
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:18">
       <c r="C56" s="1">
         <v>33011</v>
       </c>
@@ -11018,7 +11468,7 @@
         <v>3011</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>193</v>
@@ -11032,8 +11482,17 @@
       <c r="N56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:14">
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:18">
       <c r="C57" s="1">
         <v>33012</v>
       </c>
@@ -11053,7 +11512,7 @@
         <v>3012</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>193</v>
@@ -11067,8 +11526,17 @@
       <c r="N57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="3:16">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -11082,8 +11550,9 @@
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P58" s="1"/>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C59" s="1">
         <v>33112</v>
       </c>
@@ -11106,10 +11575,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -11123,8 +11592,17 @@
       <c r="O59" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:14">
+      <c r="P59" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q59" s="4">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:18">
       <c r="C60" s="1">
         <v>33108</v>
       </c>
@@ -11144,10 +11622,10 @@
         <v>3008</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="L60" s="1">
         <v>50</v>
@@ -11158,11 +11636,22 @@
       <c r="N60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" customFormat="1" customHeight="1"/>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" customHeight="1" spans="16:16">
+      <c r="P62" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 G3:K5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -497,7 +497,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="314">
   <si>
     <t>_ID</t>
   </si>
@@ -1318,6 +1318,12 @@
     <t>技能提高20%最终伤害</t>
   </si>
   <si>
+    <t>战吼·破限</t>
+  </si>
+  <si>
+    <t>额外增加2次叠加上限</t>
+  </si>
+  <si>
     <t>火球术·通神</t>
   </si>
   <si>
@@ -1369,6 +1375,9 @@
     <t>再增加60秒持续时间</t>
   </si>
   <si>
+    <t>心灵传送·破限</t>
+  </si>
+  <si>
     <t>冰爆术·哀霜Ⅱ</t>
   </si>
   <si>
@@ -1427,6 +1436,9 @@
   </si>
   <si>
     <t>再额外增加1秒持续时间</t>
+  </si>
+  <si>
+    <t>隐身道法·破限</t>
   </si>
 </sst>
 </file>
@@ -9495,7 +9507,7 @@
         <v>1001</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>255</v>
@@ -9542,7 +9554,7 @@
         <v>1002</v>
       </c>
       <c r="I7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>256</v>
@@ -9589,7 +9601,7 @@
         <v>1003</v>
       </c>
       <c r="I8" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>257</v>
@@ -9636,7 +9648,7 @@
         <v>1004</v>
       </c>
       <c r="I9" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>258</v>
@@ -9683,7 +9695,7 @@
         <v>1005</v>
       </c>
       <c r="I10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>259</v>
@@ -9730,7 +9742,7 @@
         <v>1006</v>
       </c>
       <c r="I11" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>260</v>
@@ -9777,7 +9789,7 @@
         <v>1007</v>
       </c>
       <c r="I12" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>261</v>
@@ -9824,7 +9836,7 @@
         <v>1008</v>
       </c>
       <c r="I13" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>262</v>
@@ -9871,7 +9883,7 @@
         <v>1009</v>
       </c>
       <c r="I14" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>263</v>
@@ -9918,7 +9930,7 @@
         <v>1010</v>
       </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>264</v>
@@ -9965,7 +9977,7 @@
         <v>1011</v>
       </c>
       <c r="I16" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>265</v>
@@ -10011,6 +10023,9 @@
       <c r="H17" s="3">
         <v>1012</v>
       </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
       <c r="J17" s="3" t="s">
         <v>266</v>
       </c>
@@ -10180,10 +10195,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="8:16">
-      <c r="H21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="P21" s="4"/>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C21" s="1">
+        <v>31108</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>50</v>
+      </c>
+      <c r="F21" s="1">
+        <v>20</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="8:16">
       <c r="H22" s="3"/>
@@ -10219,8 +10276,11 @@
       <c r="H25" s="3">
         <v>2001</v>
       </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
       <c r="J25" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>193</v>
@@ -10263,8 +10323,11 @@
       <c r="H26" s="3">
         <v>2002</v>
       </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
       <c r="J26" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>193</v>
@@ -10307,8 +10370,11 @@
       <c r="H27" s="3">
         <v>2003</v>
       </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
       <c r="J27" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>193</v>
@@ -10351,8 +10417,11 @@
       <c r="H28" s="3">
         <v>2004</v>
       </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
       <c r="J28" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>193</v>
@@ -10395,8 +10464,11 @@
       <c r="H29" s="3">
         <v>2005</v>
       </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
       <c r="J29" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>193</v>
@@ -10439,8 +10511,11 @@
       <c r="H30" s="3">
         <v>2006</v>
       </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
       <c r="J30" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
@@ -10483,8 +10558,11 @@
       <c r="H31" s="3">
         <v>2007</v>
       </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
       <c r="J31" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>193</v>
@@ -10527,8 +10605,11 @@
       <c r="H32" s="3">
         <v>2008</v>
       </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
       <c r="J32" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>193</v>
@@ -10571,8 +10652,11 @@
       <c r="H33" s="3">
         <v>2009</v>
       </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
       <c r="J33" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>193</v>
@@ -10615,8 +10699,11 @@
       <c r="H34" s="3">
         <v>2010</v>
       </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
       <c r="J34" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>193</v>
@@ -10659,8 +10746,11 @@
       <c r="H35" s="3">
         <v>2011</v>
       </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
       <c r="J35" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>193</v>
@@ -10703,8 +10793,11 @@
       <c r="H36" s="3">
         <v>2012</v>
       </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
       <c r="J36" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>193</v>
@@ -10755,14 +10848,17 @@
       <c r="H39" s="3">
         <v>2002</v>
       </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
       <c r="J39" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>268</v>
       </c>
       <c r="L39" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
@@ -10802,14 +10898,17 @@
       <c r="H40" s="3">
         <v>2002</v>
       </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
       <c r="J40" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L40" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
@@ -10846,14 +10945,17 @@
       <c r="H41" s="3">
         <v>2010</v>
       </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
       <c r="J41" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L41" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M41" s="1">
         <v>0</v>
@@ -10890,14 +10992,17 @@
       <c r="H42" s="3">
         <v>2008</v>
       </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
       <c r="J42" s="3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>193</v>
+        <v>274</v>
       </c>
       <c r="L42" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M42" s="1">
         <v>0</v>
@@ -10934,14 +11039,17 @@
       <c r="H43" s="3">
         <v>2007</v>
       </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
       <c r="J43" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L43" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M43" s="1">
         <v>0</v>
@@ -10978,14 +11086,17 @@
       <c r="H44" s="3">
         <v>2012</v>
       </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
       <c r="J44" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L44" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M44" s="1">
         <v>0</v>
@@ -11027,8 +11138,11 @@
       <c r="H46" s="3">
         <v>3001</v>
       </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
       <c r="J46" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>193</v>
@@ -11071,8 +11185,11 @@
       <c r="H47" s="3">
         <v>3002</v>
       </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
       <c r="J47" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>193</v>
@@ -11115,8 +11232,11 @@
       <c r="H48" s="3">
         <v>3003</v>
       </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
       <c r="J48" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>193</v>
@@ -11159,8 +11279,11 @@
       <c r="H49" s="3">
         <v>3004</v>
       </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
       <c r="J49" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>193</v>
@@ -11203,8 +11326,11 @@
       <c r="H50" s="3">
         <v>3005</v>
       </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
       <c r="J50" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>193</v>
@@ -11247,8 +11373,11 @@
       <c r="H51" s="3">
         <v>3006</v>
       </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
       <c r="J51" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>193</v>
@@ -11291,8 +11420,11 @@
       <c r="H52" s="3">
         <v>3007</v>
       </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
       <c r="J52" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>193</v>
@@ -11335,8 +11467,11 @@
       <c r="H53" s="3">
         <v>3008</v>
       </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
       <c r="J53" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>193</v>
@@ -11379,8 +11514,11 @@
       <c r="H54" s="3">
         <v>3009</v>
       </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
       <c r="J54" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>193</v>
@@ -11423,8 +11561,11 @@
       <c r="H55" s="3">
         <v>3010</v>
       </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
       <c r="J55" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>193</v>
@@ -11467,8 +11608,11 @@
       <c r="H56" s="3">
         <v>3011</v>
       </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
       <c r="J56" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>193</v>
@@ -11511,8 +11655,11 @@
       <c r="H57" s="3">
         <v>3012</v>
       </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
       <c r="J57" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>193</v>
@@ -11569,16 +11716,16 @@
         <v>3</v>
       </c>
       <c r="H59" s="3">
-        <v>1012</v>
+        <v>3012</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -11621,14 +11768,17 @@
       <c r="H60" s="3">
         <v>3008</v>
       </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
       <c r="J60" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L60" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M60" s="1">
         <v>0</v>
@@ -11643,6 +11793,53 @@
         <v>0</v>
       </c>
       <c r="R60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:18">
+      <c r="C61" s="1">
+        <v>33208</v>
+      </c>
+      <c r="D61" s="1">
+        <v>5</v>
+      </c>
+      <c r="E61" s="1">
+        <v>10</v>
+      </c>
+      <c r="F61" s="1">
+        <v>5</v>
+      </c>
+      <c r="G61" s="1">
+        <v>3</v>
+      </c>
+      <c r="H61" s="3">
+        <v>3008</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1">
+        <v>0</v>
+      </c>
+      <c r="P61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4">
+        <v>0</v>
+      </c>
+      <c r="R61" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -497,7 +497,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="317">
   <si>
     <t>_ID</t>
   </si>
@@ -1300,6 +1300,9 @@
     <t>剑二十三·通神</t>
   </si>
   <si>
+    <t>提高此技能系数30%系数增幅</t>
+  </si>
+  <si>
     <t>剑二十三·吸血</t>
   </si>
   <si>
@@ -1384,7 +1387,7 @@
     <t>使敌人受到的伤害增加20%，持续5秒</t>
   </si>
   <si>
-    <t>魔尊附体·急速</t>
+    <t>魔尊附体·双倍</t>
   </si>
   <si>
     <t>每次施法,额外获取一次加成,不能突破加成上限</t>
@@ -1430,6 +1433,12 @@
   </si>
   <si>
     <t>附带15%吸血效果</t>
+  </si>
+  <si>
+    <t>召唤白虎·复制</t>
+  </si>
+  <si>
+    <t>多召唤一只白虎</t>
   </si>
   <si>
     <t>隐身道法·神术</t>
@@ -5914,7 +5923,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -7593,7 +7602,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -8791,7 +8800,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -9301,7 +9310,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -9314,7 +9323,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:T62"/>
+  <dimension ref="C3:U63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -9323,15 +9332,18 @@
     <col min="10" max="10" width="15.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="40" style="1" customWidth="1"/>
     <col min="12" max="12" width="13.25" style="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.9166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13" style="1" customWidth="1"/>
     <col min="15" max="15" width="7.75" style="1" customWidth="1"/>
     <col min="16" max="16" width="10.375" style="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.75" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.91666666666667" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.75" style="1" customWidth="1"/>
     <col min="20" max="20" width="7.375" style="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:20">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -9380,10 +9392,17 @@
       <c r="R3" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="S3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
@@ -9432,10 +9451,17 @@
       <c r="R4" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="S4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C5" s="2" t="s">
         <v>47</v>
       </c>
@@ -9484,10 +9510,17 @@
       <c r="R5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="S5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C6" s="1">
         <v>31001</v>
       </c>
@@ -9518,23 +9551,11 @@
       <c r="L6" s="1">
         <v>50</v>
       </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C7" s="1">
         <v>31002</v>
       </c>
@@ -9565,23 +9586,11 @@
       <c r="L7" s="1">
         <v>50</v>
       </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C8" s="1">
         <v>31003</v>
       </c>
@@ -9612,23 +9621,11 @@
       <c r="L8" s="1">
         <v>50</v>
       </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C9" s="1">
         <v>31004</v>
       </c>
@@ -9659,23 +9656,11 @@
       <c r="L9" s="1">
         <v>50</v>
       </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C10" s="1">
         <v>31005</v>
       </c>
@@ -9706,23 +9691,11 @@
       <c r="L10" s="1">
         <v>50</v>
       </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="Q10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C11" s="1">
         <v>31006</v>
       </c>
@@ -9753,23 +9726,11 @@
       <c r="L11" s="1">
         <v>50</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="Q11" s="4"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C12" s="1">
         <v>31007</v>
       </c>
@@ -9800,23 +9761,11 @@
       <c r="L12" s="1">
         <v>50</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="Q12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C13" s="1">
         <v>31008</v>
       </c>
@@ -9847,23 +9796,11 @@
       <c r="L13" s="1">
         <v>50</v>
       </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C14" s="1">
         <v>31009</v>
       </c>
@@ -9894,23 +9831,11 @@
       <c r="L14" s="1">
         <v>50</v>
       </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="Q14" s="4"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C15" s="1">
         <v>31010</v>
       </c>
@@ -9941,23 +9866,11 @@
       <c r="L15" s="1">
         <v>50</v>
       </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="Q15" s="4"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C16" s="1">
         <v>31011</v>
       </c>
@@ -9988,23 +9901,11 @@
       <c r="L16" s="1">
         <v>50</v>
       </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="4">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:18">
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="Q16" s="4"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:17">
       <c r="C17" s="1">
         <v>31012</v>
       </c>
@@ -10030,28 +9931,16 @@
         <v>266</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>193</v>
+        <v>267</v>
       </c>
       <c r="L17" s="1">
-        <v>50</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:18">
+        <v>30</v>
+      </c>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C18" s="1">
         <v>31112</v>
       </c>
@@ -10074,34 +9963,23 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
       <c r="O18" s="1">
         <v>101</v>
       </c>
       <c r="P18" s="1">
         <v>10</v>
       </c>
-      <c r="Q18" s="4">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="Q18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C19" s="1">
         <v>31212</v>
       </c>
@@ -10124,31 +10002,19 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="L19" s="1"/>
       <c r="M19" s="1">
         <v>20</v>
       </c>
-      <c r="N19" s="1">
-        <v>0</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="4">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="N19" s="1"/>
+      <c r="Q19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C20" s="1">
         <v>31312</v>
       </c>
@@ -10171,31 +10037,19 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
       <c r="N20" s="1">
         <v>20</v>
       </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="Q20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C21" s="1">
         <v>31108</v>
       </c>
@@ -10218,28 +10072,18 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
+        <v>275</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="8:16">
@@ -10257,7 +10101,7 @@
       <c r="J24" s="3"/>
       <c r="P24" s="4"/>
     </row>
-    <row r="25" customHeight="1" spans="3:18">
+    <row r="25" customHeight="1" spans="3:17">
       <c r="C25" s="1">
         <v>32001</v>
       </c>
@@ -10280,7 +10124,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>193</v>
@@ -10288,23 +10132,11 @@
       <c r="L25" s="1">
         <v>50</v>
       </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="4">
-        <v>0</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:18">
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="Q25" s="4"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:17">
       <c r="C26" s="1">
         <v>32002</v>
       </c>
@@ -10327,7 +10159,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>193</v>
@@ -10335,23 +10167,11 @@
       <c r="L26" s="1">
         <v>50</v>
       </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4">
-        <v>0</v>
-      </c>
-      <c r="R26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:18">
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="Q26" s="4"/>
+    </row>
+    <row r="27" customHeight="1" spans="3:17">
       <c r="C27" s="1">
         <v>32003</v>
       </c>
@@ -10374,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>193</v>
@@ -10382,23 +10202,11 @@
       <c r="L27" s="1">
         <v>50</v>
       </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:18">
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="Q27" s="4"/>
+    </row>
+    <row r="28" customHeight="1" spans="3:17">
       <c r="C28" s="1">
         <v>32004</v>
       </c>
@@ -10421,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>193</v>
@@ -10429,23 +10237,11 @@
       <c r="L28" s="1">
         <v>50</v>
       </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="4">
-        <v>0</v>
-      </c>
-      <c r="R28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:18">
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="Q28" s="4"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:17">
       <c r="C29" s="1">
         <v>32005</v>
       </c>
@@ -10468,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>193</v>
@@ -10476,23 +10272,11 @@
       <c r="L29" s="1">
         <v>50</v>
       </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1">
-        <v>0</v>
-      </c>
-      <c r="P29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="4">
-        <v>0</v>
-      </c>
-      <c r="R29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:18">
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="Q29" s="4"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:17">
       <c r="C30" s="1">
         <v>32006</v>
       </c>
@@ -10515,7 +10299,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
@@ -10523,23 +10307,11 @@
       <c r="L30" s="1">
         <v>50</v>
       </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1">
-        <v>0</v>
-      </c>
-      <c r="P30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="4">
-        <v>0</v>
-      </c>
-      <c r="R30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:18">
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="Q30" s="4"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:17">
       <c r="C31" s="1">
         <v>32007</v>
       </c>
@@ -10562,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>193</v>
@@ -10570,23 +10342,11 @@
       <c r="L31" s="1">
         <v>50</v>
       </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="4">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:18">
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="Q31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:17">
       <c r="C32" s="1">
         <v>32008</v>
       </c>
@@ -10609,7 +10369,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>193</v>
@@ -10617,23 +10377,11 @@
       <c r="L32" s="1">
         <v>50</v>
       </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="4">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:18">
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="Q32" s="4"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:17">
       <c r="C33" s="1">
         <v>32009</v>
       </c>
@@ -10656,7 +10404,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>193</v>
@@ -10664,23 +10412,11 @@
       <c r="L33" s="1">
         <v>50</v>
       </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="4">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:18">
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="Q33" s="4"/>
+    </row>
+    <row r="34" customHeight="1" spans="3:17">
       <c r="C34" s="1">
         <v>32010</v>
       </c>
@@ -10703,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>193</v>
@@ -10711,23 +10447,11 @@
       <c r="L34" s="1">
         <v>50</v>
       </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="P34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="4">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:18">
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="Q34" s="4"/>
+    </row>
+    <row r="35" customHeight="1" spans="3:17">
       <c r="C35" s="1">
         <v>32011</v>
       </c>
@@ -10750,7 +10474,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>193</v>
@@ -10758,23 +10482,11 @@
       <c r="L35" s="1">
         <v>50</v>
       </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1">
-        <v>0</v>
-      </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="4">
-        <v>0</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:18">
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="Q35" s="4"/>
+    </row>
+    <row r="36" customHeight="1" spans="3:17">
       <c r="C36" s="1">
         <v>32012</v>
       </c>
@@ -10797,29 +10509,17 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>193</v>
+        <v>267</v>
       </c>
       <c r="L36" s="1">
-        <v>50</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="4">
-        <v>0</v>
-      </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="Q36" s="4"/>
     </row>
     <row r="37" customHeight="1" spans="8:10">
       <c r="H37" s="3"/>
@@ -10829,7 +10529,7 @@
       <c r="H38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="3:18">
+    <row r="39" customHeight="1" spans="3:17">
       <c r="C39" s="1">
         <v>32102</v>
       </c>
@@ -10852,34 +10552,23 @@
         <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
       <c r="O39" s="1">
         <v>101</v>
       </c>
       <c r="P39" s="1">
         <v>10</v>
       </c>
-      <c r="Q39" s="4">
-        <v>0</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:18">
+      <c r="Q39" s="4"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:19">
       <c r="C40" s="1">
         <v>32202</v>
       </c>
@@ -10902,31 +10591,21 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="4">
-        <v>0</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:18">
+        <v>290</v>
+      </c>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:20">
       <c r="C41" s="1">
         <v>32110</v>
       </c>
@@ -10949,31 +10628,22 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="4">
-        <v>0</v>
-      </c>
-      <c r="R41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:18">
+        <v>292</v>
+      </c>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:19">
       <c r="C42" s="1">
         <v>32108</v>
       </c>
@@ -10996,31 +10666,21 @@
         <v>0</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="4">
-        <v>0</v>
-      </c>
-      <c r="R42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:18">
+        <v>275</v>
+      </c>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:17">
       <c r="C43" s="1">
         <v>32107</v>
       </c>
@@ -11043,31 +10703,23 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="L43" s="1">
-        <v>0</v>
-      </c>
-      <c r="M43" s="1">
-        <v>0</v>
-      </c>
-      <c r="N43" s="1">
-        <v>0</v>
+        <v>295</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1">
+        <v>17</v>
       </c>
       <c r="P43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="4">
-        <v>0</v>
-      </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:18">
+        <v>30</v>
+      </c>
+      <c r="Q43" s="4"/>
+    </row>
+    <row r="44" customHeight="1" spans="3:19">
       <c r="C44" s="1">
         <v>32112</v>
       </c>
@@ -11090,28 +10742,18 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="4">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
+        <v>297</v>
+      </c>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="8:11">
@@ -11119,7 +10761,7 @@
       <c r="J45" s="3"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="3:18">
+    <row r="46" customHeight="1" spans="3:17">
       <c r="C46" s="1">
         <v>33001</v>
       </c>
@@ -11142,7 +10784,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>193</v>
@@ -11150,23 +10792,11 @@
       <c r="L46" s="1">
         <v>50</v>
       </c>
-      <c r="M46" s="1">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="4">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:18">
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="Q46" s="4"/>
+    </row>
+    <row r="47" customHeight="1" spans="3:17">
       <c r="C47" s="1">
         <v>33002</v>
       </c>
@@ -11189,7 +10819,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>193</v>
@@ -11197,23 +10827,11 @@
       <c r="L47" s="1">
         <v>50</v>
       </c>
-      <c r="M47" s="1">
-        <v>0</v>
-      </c>
-      <c r="N47" s="1">
-        <v>0</v>
-      </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="4">
-        <v>0</v>
-      </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:18">
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="Q47" s="4"/>
+    </row>
+    <row r="48" customHeight="1" spans="3:17">
       <c r="C48" s="1">
         <v>33003</v>
       </c>
@@ -11236,7 +10854,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>193</v>
@@ -11244,23 +10862,11 @@
       <c r="L48" s="1">
         <v>50</v>
       </c>
-      <c r="M48" s="1">
-        <v>0</v>
-      </c>
-      <c r="N48" s="1">
-        <v>0</v>
-      </c>
-      <c r="P48" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="4">
-        <v>0</v>
-      </c>
-      <c r="R48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:18">
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="Q48" s="4"/>
+    </row>
+    <row r="49" customHeight="1" spans="3:17">
       <c r="C49" s="1">
         <v>33004</v>
       </c>
@@ -11283,7 +10889,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>193</v>
@@ -11291,23 +10897,11 @@
       <c r="L49" s="1">
         <v>50</v>
       </c>
-      <c r="M49" s="1">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="4">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:18">
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="Q49" s="4"/>
+    </row>
+    <row r="50" customHeight="1" spans="3:17">
       <c r="C50" s="1">
         <v>33005</v>
       </c>
@@ -11330,7 +10924,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>193</v>
@@ -11338,23 +10932,11 @@
       <c r="L50" s="1">
         <v>50</v>
       </c>
-      <c r="M50" s="1">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="4">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:18">
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="Q50" s="4"/>
+    </row>
+    <row r="51" customHeight="1" spans="3:17">
       <c r="C51" s="1">
         <v>33006</v>
       </c>
@@ -11377,7 +10959,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>193</v>
@@ -11385,23 +10967,11 @@
       <c r="L51" s="1">
         <v>50</v>
       </c>
-      <c r="M51" s="1">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="4">
-        <v>0</v>
-      </c>
-      <c r="R51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:18">
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="Q51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:17">
       <c r="C52" s="1">
         <v>33007</v>
       </c>
@@ -11424,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>193</v>
@@ -11432,23 +11002,11 @@
       <c r="L52" s="1">
         <v>50</v>
       </c>
-      <c r="M52" s="1">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="4">
-        <v>0</v>
-      </c>
-      <c r="R52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:18">
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="Q52" s="4"/>
+    </row>
+    <row r="53" customHeight="1" spans="3:17">
       <c r="C53" s="1">
         <v>33008</v>
       </c>
@@ -11471,7 +11029,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>193</v>
@@ -11479,23 +11037,11 @@
       <c r="L53" s="1">
         <v>50</v>
       </c>
-      <c r="M53" s="1">
-        <v>0</v>
-      </c>
-      <c r="N53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="4">
-        <v>0</v>
-      </c>
-      <c r="R53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:18">
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="Q53" s="4"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:17">
       <c r="C54" s="1">
         <v>33009</v>
       </c>
@@ -11518,7 +11064,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>193</v>
@@ -11526,23 +11072,11 @@
       <c r="L54" s="1">
         <v>50</v>
       </c>
-      <c r="M54" s="1">
-        <v>0</v>
-      </c>
-      <c r="N54" s="1">
-        <v>0</v>
-      </c>
-      <c r="P54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="4">
-        <v>0</v>
-      </c>
-      <c r="R54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:18">
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="Q54" s="4"/>
+    </row>
+    <row r="55" customHeight="1" spans="3:17">
       <c r="C55" s="1">
         <v>33010</v>
       </c>
@@ -11565,7 +11099,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>193</v>
@@ -11573,23 +11107,11 @@
       <c r="L55" s="1">
         <v>50</v>
       </c>
-      <c r="M55" s="1">
-        <v>0</v>
-      </c>
-      <c r="N55" s="1">
-        <v>0</v>
-      </c>
-      <c r="P55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="4">
-        <v>0</v>
-      </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:18">
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="Q55" s="4"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:17">
       <c r="C56" s="1">
         <v>33011</v>
       </c>
@@ -11612,7 +11134,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>193</v>
@@ -11620,23 +11142,11 @@
       <c r="L56" s="1">
         <v>50</v>
       </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1">
-        <v>0</v>
-      </c>
-      <c r="P56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="4">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:18">
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="Q56" s="4"/>
+    </row>
+    <row r="57" customHeight="1" spans="3:17">
       <c r="C57" s="1">
         <v>33012</v>
       </c>
@@ -11659,29 +11169,17 @@
         <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>193</v>
+        <v>267</v>
       </c>
       <c r="L57" s="1">
-        <v>50</v>
-      </c>
-      <c r="M57" s="1">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="4">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="Q57" s="4"/>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:16">
       <c r="C58" s="1"/>
@@ -11699,7 +11197,7 @@
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C59" s="1">
         <v>33112</v>
       </c>
@@ -11722,36 +11220,25 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="L59" s="1">
-        <v>0</v>
-      </c>
-      <c r="M59" s="1">
-        <v>0</v>
-      </c>
-      <c r="N59" s="1">
-        <v>0</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
       <c r="O59" s="1">
         <v>101</v>
       </c>
       <c r="P59" s="1">
         <v>15</v>
       </c>
-      <c r="Q59" s="4">
-        <v>0</v>
-      </c>
-      <c r="R59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:18">
+      <c r="Q59" s="4"/>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C60" s="1">
-        <v>33108</v>
+        <v>33212</v>
       </c>
       <c r="D60" s="1">
         <v>5</v>
@@ -11760,45 +11247,37 @@
         <v>10</v>
       </c>
       <c r="F60" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G60" s="1">
         <v>3</v>
       </c>
       <c r="H60" s="3">
-        <v>3008</v>
+        <v>3012</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="L60" s="1">
-        <v>0</v>
-      </c>
-      <c r="M60" s="1">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1">
-        <v>0</v>
-      </c>
-      <c r="P60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="4">
-        <v>0</v>
-      </c>
-      <c r="R60" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:18">
+        <v>313</v>
+      </c>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:20">
       <c r="C61" s="1">
-        <v>33208</v>
+        <v>33108</v>
       </c>
       <c r="D61" s="1">
         <v>5</v>
@@ -11819,36 +11298,64 @@
         <v>0</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="L61" s="1">
-        <v>0</v>
-      </c>
-      <c r="M61" s="1">
-        <v>0</v>
-      </c>
-      <c r="N61" s="1">
-        <v>0</v>
-      </c>
-      <c r="P61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="4">
-        <v>0</v>
-      </c>
-      <c r="R61" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" customHeight="1" spans="16:16">
-      <c r="P62" s="1"/>
+        <v>315</v>
+      </c>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:19">
+      <c r="C62" s="1">
+        <v>33208</v>
+      </c>
+      <c r="D62" s="1">
+        <v>5</v>
+      </c>
+      <c r="E62" s="1">
+        <v>10</v>
+      </c>
+      <c r="F62" s="1">
+        <v>5</v>
+      </c>
+      <c r="G62" s="1">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
+        <v>3008</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="16:16">
+      <c r="P63" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="U3:U5 C3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -497,7 +497,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="318">
   <si>
     <t>_ID</t>
   </si>
@@ -1427,6 +1427,9 @@
   </si>
   <si>
     <t>召唤白虎·通神</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>召唤白虎·吸血</t>
@@ -9323,7 +9326,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:U63"/>
+  <dimension ref="A3:U63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -11197,7 +11200,13 @@
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A59" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>310</v>
+      </c>
       <c r="C59" s="1">
         <v>33112</v>
       </c>
@@ -11220,10 +11229,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -11259,10 +11268,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
@@ -11298,10 +11307,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
@@ -11336,7 +11345,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>275</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -3465,7 +3465,7 @@
         <v>80</v>
       </c>
       <c r="D16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -3542,7 +3542,7 @@
         <v>83</v>
       </c>
       <c r="D17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -4543,7 +4543,7 @@
         <v>114</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -4620,7 +4620,7 @@
         <v>115</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5621,7 +5621,7 @@
         <v>146</v>
       </c>
       <c r="D44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -5698,7 +5698,7 @@
         <v>147</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -9939,8 +9939,6 @@
       <c r="L17" s="1">
         <v>30</v>
       </c>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
       <c r="Q17" s="4"/>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -10135,8 +10133,6 @@
       <c r="L25" s="1">
         <v>50</v>
       </c>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
       <c r="Q25" s="4"/>
     </row>
     <row r="26" customHeight="1" spans="3:17">
@@ -10170,8 +10166,6 @@
       <c r="L26" s="1">
         <v>50</v>
       </c>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
       <c r="Q26" s="4"/>
     </row>
     <row r="27" customHeight="1" spans="3:17">
@@ -10205,8 +10199,6 @@
       <c r="L27" s="1">
         <v>50</v>
       </c>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
       <c r="Q27" s="4"/>
     </row>
     <row r="28" customHeight="1" spans="3:17">
@@ -10240,8 +10232,6 @@
       <c r="L28" s="1">
         <v>50</v>
       </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
       <c r="Q28" s="4"/>
     </row>
     <row r="29" customHeight="1" spans="3:17">
@@ -10275,8 +10265,6 @@
       <c r="L29" s="1">
         <v>50</v>
       </c>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
       <c r="Q29" s="4"/>
     </row>
     <row r="30" customHeight="1" spans="3:17">
@@ -10310,8 +10298,6 @@
       <c r="L30" s="1">
         <v>50</v>
       </c>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
       <c r="Q30" s="4"/>
     </row>
     <row r="31" customHeight="1" spans="3:17">
@@ -10345,8 +10331,6 @@
       <c r="L31" s="1">
         <v>50</v>
       </c>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
       <c r="Q31" s="4"/>
     </row>
     <row r="32" customHeight="1" spans="3:17">
@@ -10380,8 +10364,6 @@
       <c r="L32" s="1">
         <v>50</v>
       </c>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
       <c r="Q32" s="4"/>
     </row>
     <row r="33" customHeight="1" spans="3:17">
@@ -10415,8 +10397,6 @@
       <c r="L33" s="1">
         <v>50</v>
       </c>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
       <c r="Q33" s="4"/>
     </row>
     <row r="34" customHeight="1" spans="3:17">
@@ -10450,8 +10430,6 @@
       <c r="L34" s="1">
         <v>50</v>
       </c>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
       <c r="Q34" s="4"/>
     </row>
     <row r="35" customHeight="1" spans="3:17">
@@ -10485,8 +10463,6 @@
       <c r="L35" s="1">
         <v>50</v>
       </c>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
       <c r="Q35" s="4"/>
     </row>
     <row r="36" customHeight="1" spans="3:17">
@@ -10520,8 +10496,6 @@
       <c r="L36" s="1">
         <v>30</v>
       </c>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
       <c r="Q36" s="4"/>
     </row>
     <row r="37" customHeight="1" spans="8:10">
@@ -10560,9 +10534,6 @@
       <c r="K39" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
       <c r="O39" s="1">
         <v>101</v>
       </c>
@@ -10599,11 +10570,7 @@
       <c r="K40" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
       <c r="Q40" s="4"/>
-      <c r="R40" s="1"/>
       <c r="S40" s="1">
         <v>1</v>
       </c>
@@ -10636,12 +10603,7 @@
       <c r="K41" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
       <c r="Q41" s="4"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
       <c r="T41" s="1">
         <v>60</v>
       </c>
@@ -10674,11 +10636,7 @@
       <c r="K42" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
       <c r="Q42" s="4"/>
-      <c r="R42" s="1"/>
       <c r="S42" s="1">
         <v>2</v>
       </c>
@@ -10711,9 +10669,6 @@
       <c r="K43" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
       <c r="O43" s="1">
         <v>17</v>
       </c>
@@ -10750,11 +10705,7 @@
       <c r="K44" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
       <c r="Q44" s="4"/>
-      <c r="R44" s="1"/>
       <c r="S44" s="1">
         <v>1</v>
       </c>
@@ -10795,8 +10746,6 @@
       <c r="L46" s="1">
         <v>50</v>
       </c>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
       <c r="Q46" s="4"/>
     </row>
     <row r="47" customHeight="1" spans="3:17">
@@ -10830,8 +10779,6 @@
       <c r="L47" s="1">
         <v>50</v>
       </c>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
       <c r="Q47" s="4"/>
     </row>
     <row r="48" customHeight="1" spans="3:17">
@@ -10865,8 +10812,6 @@
       <c r="L48" s="1">
         <v>50</v>
       </c>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
       <c r="Q48" s="4"/>
     </row>
     <row r="49" customHeight="1" spans="3:17">
@@ -10900,8 +10845,6 @@
       <c r="L49" s="1">
         <v>50</v>
       </c>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
       <c r="Q49" s="4"/>
     </row>
     <row r="50" customHeight="1" spans="3:17">
@@ -10935,8 +10878,6 @@
       <c r="L50" s="1">
         <v>50</v>
       </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
       <c r="Q50" s="4"/>
     </row>
     <row r="51" customHeight="1" spans="3:17">
@@ -10970,8 +10911,6 @@
       <c r="L51" s="1">
         <v>50</v>
       </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
       <c r="Q51" s="4"/>
     </row>
     <row r="52" customHeight="1" spans="3:17">
@@ -11005,8 +10944,6 @@
       <c r="L52" s="1">
         <v>50</v>
       </c>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
       <c r="Q52" s="4"/>
     </row>
     <row r="53" customHeight="1" spans="3:17">
@@ -11040,8 +10977,6 @@
       <c r="L53" s="1">
         <v>50</v>
       </c>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
       <c r="Q53" s="4"/>
     </row>
     <row r="54" customHeight="1" spans="3:17">
@@ -11075,8 +11010,6 @@
       <c r="L54" s="1">
         <v>50</v>
       </c>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
       <c r="Q54" s="4"/>
     </row>
     <row r="55" customHeight="1" spans="3:17">
@@ -11110,8 +11043,6 @@
       <c r="L55" s="1">
         <v>50</v>
       </c>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
       <c r="Q55" s="4"/>
     </row>
     <row r="56" customHeight="1" spans="3:17">
@@ -11145,8 +11076,6 @@
       <c r="L56" s="1">
         <v>50</v>
       </c>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
       <c r="Q56" s="4"/>
     </row>
     <row r="57" customHeight="1" spans="3:17">
@@ -11180,8 +11109,6 @@
       <c r="L57" s="1">
         <v>30</v>
       </c>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
       <c r="Q57" s="4"/>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:16">
@@ -11312,12 +11239,7 @@
       <c r="K61" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
       <c r="Q61" s="4"/>
-      <c r="R61" s="1"/>
-      <c r="S61" s="1"/>
       <c r="T61" s="1">
         <v>1</v>
       </c>
@@ -11350,11 +11272,7 @@
       <c r="K62" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
       <c r="Q62" s="4"/>
-      <c r="R62" s="1"/>
       <c r="S62" s="1">
         <v>2</v>
       </c>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -497,7 +497,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="318">
   <si>
     <t>_ID</t>
   </si>
@@ -2690,7 +2690,7 @@
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
     </row>
-    <row r="6" s="4" customFormat="1" customHeight="1" spans="3:27">
+    <row r="6" s="4" customFormat="1" customHeight="1" spans="3:29">
       <c r="C6" s="1" t="s">
         <v>49</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" customHeight="1" spans="3:27">
+    <row r="7" s="4" customFormat="1" customHeight="1" spans="3:29">
       <c r="C7" s="1" t="s">
         <v>56</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" customHeight="1" spans="3:27">
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="3:29">
       <c r="C8" s="1" t="s">
         <v>59</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" customHeight="1" spans="3:27">
+    <row r="9" s="4" customFormat="1" customHeight="1" spans="3:29">
       <c r="C9" s="1" t="s">
         <v>62</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:27">
+    <row r="10" customHeight="1" spans="3:29">
       <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:27">
+    <row r="11" customHeight="1" spans="3:29">
       <c r="C11" s="1" t="s">
         <v>67</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:27">
+    <row r="12" customHeight="1" spans="3:29">
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:27">
+    <row r="13" customHeight="1" spans="3:29">
       <c r="C13" s="1" t="s">
         <v>72</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:27">
+    <row r="14" customHeight="1" spans="3:29">
       <c r="C14" s="1" t="s">
         <v>74</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:27">
+    <row r="15" customHeight="1" spans="3:29">
       <c r="C15" s="1">
         <v>10010</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:27">
+    <row r="16" customHeight="1" spans="3:29">
       <c r="C16" s="1" t="s">
         <v>80</v>
       </c>
@@ -7751,7 +7751,7 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C6" s="1">
         <v>11001</v>
       </c>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="P6" s="4"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C7" s="1">
         <v>11002</v>
       </c>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="P7" s="4"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C8" s="1">
         <v>11003</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C9" s="1">
         <v>11004</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C10" s="1">
         <v>11005</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C11" s="1">
         <v>11006</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C12" s="1">
         <v>11007</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C13" s="1">
         <v>11008</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C14" s="1">
         <v>11009</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C15" s="1">
         <v>11010</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C16" s="1">
         <v>11110</v>
       </c>
@@ -8105,15 +8105,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="11:12">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="11:12">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="11:12">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
@@ -8469,16 +8469,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="12:12">
+    <row r="31" customHeight="1" spans="3:12">
       <c r="L31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="12:12">
+    <row r="32" customHeight="1" spans="3:12">
       <c r="L32" s="4"/>
     </row>
-    <row r="33" customHeight="1" spans="12:12">
+    <row r="33" customHeight="1" spans="3:12">
       <c r="L33" s="4"/>
     </row>
-    <row r="34" customHeight="1" spans="12:12">
+    <row r="34" customHeight="1" spans="3:12">
       <c r="L34" s="4"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -8957,7 +8957,7 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C6" s="1">
         <v>21001</v>
       </c>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C7" s="1">
         <v>21002</v>
       </c>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C8" s="1">
         <v>21003</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C9" s="1">
         <v>21004</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C10" s="1">
         <v>21005</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C11" s="1">
         <v>21006</v>
       </c>
@@ -9151,7 +9151,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C12" s="1">
         <v>21007</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C13" s="1">
         <v>21008</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C14" s="1">
         <v>21009</v>
       </c>
@@ -9247,7 +9247,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C15" s="1">
         <v>21010</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C16" s="1">
         <v>21011</v>
       </c>
@@ -9326,7 +9326,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:U63"/>
+  <dimension ref="A3:V63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -9343,10 +9343,12 @@
     <col min="18" max="18" width="8.91666666666667" style="1" customWidth="1"/>
     <col min="19" max="19" width="13.75" style="1" customWidth="1"/>
     <col min="20" max="20" width="7.375" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="1"/>
+    <col min="21" max="21" width="9" style="1"/>
+    <col min="22" max="22" width="7.875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:21">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -9404,8 +9406,11 @@
       <c r="U3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
@@ -9463,8 +9468,11 @@
       <c r="U4" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V4" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C5" s="2" t="s">
         <v>47</v>
       </c>
@@ -9522,8 +9530,11 @@
       <c r="U5" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="V5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C6" s="1">
         <v>31001</v>
       </c>
@@ -9558,7 +9569,7 @@
       <c r="N6" s="1"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C7" s="1">
         <v>31002</v>
       </c>
@@ -9593,7 +9604,7 @@
       <c r="N7" s="1"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C8" s="1">
         <v>31003</v>
       </c>
@@ -9628,7 +9639,7 @@
       <c r="N8" s="1"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C9" s="1">
         <v>31004</v>
       </c>
@@ -9663,7 +9674,7 @@
       <c r="N9" s="1"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C10" s="1">
         <v>31005</v>
       </c>
@@ -9698,7 +9709,7 @@
       <c r="N10" s="1"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C11" s="1">
         <v>31006</v>
       </c>
@@ -9733,7 +9744,7 @@
       <c r="N11" s="1"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C12" s="1">
         <v>31007</v>
       </c>
@@ -9768,7 +9779,7 @@
       <c r="N12" s="1"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C13" s="1">
         <v>31008</v>
       </c>
@@ -9803,7 +9814,7 @@
       <c r="N13" s="1"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C14" s="1">
         <v>31009</v>
       </c>
@@ -9838,7 +9849,7 @@
       <c r="N14" s="1"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C15" s="1">
         <v>31010</v>
       </c>
@@ -9873,7 +9884,7 @@
       <c r="N15" s="1"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C16" s="1">
         <v>31011</v>
       </c>
@@ -9908,7 +9919,7 @@
       <c r="N16" s="1"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" customHeight="1" spans="3:17">
+    <row r="17" customHeight="1" spans="3:22">
       <c r="C17" s="1">
         <v>31012</v>
       </c>
@@ -9941,7 +9952,7 @@
       </c>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C18" s="1">
         <v>31112</v>
       </c>
@@ -9980,7 +9991,7 @@
       </c>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C19" s="1">
         <v>31212</v>
       </c>
@@ -10015,7 +10026,7 @@
       <c r="N19" s="1"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C20" s="1">
         <v>31312</v>
       </c>
@@ -10050,7 +10061,7 @@
       </c>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C21" s="1">
         <v>31108</v>
       </c>
@@ -10086,23 +10097,26 @@
       <c r="S21" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="8:16">
+      <c r="V21" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:22">
       <c r="H22" s="3"/>
       <c r="J22" s="3"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" customHeight="1" spans="8:16">
+    <row r="23" customHeight="1" spans="3:22">
       <c r="H23" s="3"/>
       <c r="J23" s="3"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" customHeight="1" spans="8:16">
+    <row r="24" customHeight="1" spans="3:22">
       <c r="H24" s="3"/>
       <c r="J24" s="3"/>
       <c r="P24" s="4"/>
     </row>
-    <row r="25" customHeight="1" spans="3:17">
+    <row r="25" customHeight="1" spans="3:22">
       <c r="C25" s="1">
         <v>32001</v>
       </c>
@@ -10135,7 +10149,7 @@
       </c>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" customHeight="1" spans="3:17">
+    <row r="26" customHeight="1" spans="3:22">
       <c r="C26" s="1">
         <v>32002</v>
       </c>
@@ -10168,7 +10182,7 @@
       </c>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" customHeight="1" spans="3:17">
+    <row r="27" customHeight="1" spans="3:22">
       <c r="C27" s="1">
         <v>32003</v>
       </c>
@@ -10201,7 +10215,7 @@
       </c>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" customHeight="1" spans="3:17">
+    <row r="28" customHeight="1" spans="3:22">
       <c r="C28" s="1">
         <v>32004</v>
       </c>
@@ -10234,7 +10248,7 @@
       </c>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" customHeight="1" spans="3:17">
+    <row r="29" customHeight="1" spans="3:22">
       <c r="C29" s="1">
         <v>32005</v>
       </c>
@@ -10267,7 +10281,7 @@
       </c>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" customHeight="1" spans="3:17">
+    <row r="30" customHeight="1" spans="3:22">
       <c r="C30" s="1">
         <v>32006</v>
       </c>
@@ -10300,7 +10314,7 @@
       </c>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" customHeight="1" spans="3:17">
+    <row r="31" customHeight="1" spans="3:22">
       <c r="C31" s="1">
         <v>32007</v>
       </c>
@@ -10333,7 +10347,7 @@
       </c>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="3:17">
+    <row r="32" customHeight="1" spans="3:22">
       <c r="C32" s="1">
         <v>32008</v>
       </c>
@@ -10366,7 +10380,7 @@
       </c>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" customHeight="1" spans="3:17">
+    <row r="33" customHeight="1" spans="3:22">
       <c r="C33" s="1">
         <v>32009</v>
       </c>
@@ -10399,7 +10413,7 @@
       </c>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" customHeight="1" spans="3:17">
+    <row r="34" customHeight="1" spans="3:22">
       <c r="C34" s="1">
         <v>32010</v>
       </c>
@@ -10432,7 +10446,7 @@
       </c>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" customHeight="1" spans="3:17">
+    <row r="35" customHeight="1" spans="3:22">
       <c r="C35" s="1">
         <v>32011</v>
       </c>
@@ -10465,7 +10479,7 @@
       </c>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" customHeight="1" spans="3:17">
+    <row r="36" customHeight="1" spans="3:22">
       <c r="C36" s="1">
         <v>32012</v>
       </c>
@@ -10498,15 +10512,15 @@
       </c>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" customHeight="1" spans="8:10">
+    <row r="37" customHeight="1" spans="3:22">
       <c r="H37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" customHeight="1" spans="8:10">
+    <row r="38" customHeight="1" spans="3:22">
       <c r="H38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="3:17">
+    <row r="39" customHeight="1" spans="3:22">
       <c r="C39" s="1">
         <v>32102</v>
       </c>
@@ -10542,7 +10556,7 @@
       </c>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" customHeight="1" spans="3:19">
+    <row r="40" customHeight="1" spans="3:22">
       <c r="C40" s="1">
         <v>32202</v>
       </c>
@@ -10575,7 +10589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:20">
+    <row r="41" customHeight="1" spans="3:22">
       <c r="C41" s="1">
         <v>32110</v>
       </c>
@@ -10608,7 +10622,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:19">
+    <row r="42" customHeight="1" spans="3:22">
       <c r="C42" s="1">
         <v>32108</v>
       </c>
@@ -10640,8 +10654,11 @@
       <c r="S42" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:17">
+      <c r="V42" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:22">
       <c r="C43" s="1">
         <v>32107</v>
       </c>
@@ -10677,7 +10694,7 @@
       </c>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" customHeight="1" spans="3:19">
+    <row r="44" customHeight="1" spans="3:22">
       <c r="C44" s="1">
         <v>32112</v>
       </c>
@@ -10710,12 +10727,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="8:11">
+    <row r="45" customHeight="1" spans="3:22">
       <c r="H45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="3:17">
+    <row r="46" customHeight="1" spans="3:22">
       <c r="C46" s="1">
         <v>33001</v>
       </c>
@@ -10748,7 +10765,7 @@
       </c>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" customHeight="1" spans="3:17">
+    <row r="47" customHeight="1" spans="3:22">
       <c r="C47" s="1">
         <v>33002</v>
       </c>
@@ -10781,7 +10798,7 @@
       </c>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" customHeight="1" spans="3:17">
+    <row r="48" customHeight="1" spans="3:22">
       <c r="C48" s="1">
         <v>33003</v>
       </c>
@@ -10814,7 +10831,7 @@
       </c>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" customHeight="1" spans="3:17">
+    <row r="49" customHeight="1" spans="1:22">
       <c r="C49" s="1">
         <v>33004</v>
       </c>
@@ -10847,7 +10864,7 @@
       </c>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" customHeight="1" spans="3:17">
+    <row r="50" customHeight="1" spans="1:22">
       <c r="C50" s="1">
         <v>33005</v>
       </c>
@@ -10880,7 +10897,7 @@
       </c>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" customHeight="1" spans="3:17">
+    <row r="51" customHeight="1" spans="1:22">
       <c r="C51" s="1">
         <v>33006</v>
       </c>
@@ -10913,7 +10930,7 @@
       </c>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" customHeight="1" spans="3:17">
+    <row r="52" customHeight="1" spans="1:22">
       <c r="C52" s="1">
         <v>33007</v>
       </c>
@@ -10946,7 +10963,7 @@
       </c>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" customHeight="1" spans="3:17">
+    <row r="53" customHeight="1" spans="1:22">
       <c r="C53" s="1">
         <v>33008</v>
       </c>
@@ -10979,7 +10996,7 @@
       </c>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" customHeight="1" spans="3:17">
+    <row r="54" customHeight="1" spans="1:22">
       <c r="C54" s="1">
         <v>33009</v>
       </c>
@@ -11012,7 +11029,7 @@
       </c>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" customHeight="1" spans="3:17">
+    <row r="55" customHeight="1" spans="1:22">
       <c r="C55" s="1">
         <v>33010</v>
       </c>
@@ -11045,7 +11062,7 @@
       </c>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" customHeight="1" spans="3:17">
+    <row r="56" customHeight="1" spans="1:22">
       <c r="C56" s="1">
         <v>33011</v>
       </c>
@@ -11078,7 +11095,7 @@
       </c>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" customHeight="1" spans="3:17">
+    <row r="57" customHeight="1" spans="1:22">
       <c r="C57" s="1">
         <v>33012</v>
       </c>
@@ -11111,7 +11128,7 @@
       </c>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="3:16">
+    <row r="58" customFormat="1" customHeight="1" spans="1:22">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -11126,8 +11143,9 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="V58" s="1"/>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A59" s="1" t="s">
         <v>310</v>
       </c>
@@ -11172,7 +11190,7 @@
       </c>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C60" s="1">
         <v>33212</v>
       </c>
@@ -11211,7 +11229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="3:20">
+    <row r="61" customHeight="1" spans="1:22">
       <c r="C61" s="1">
         <v>33108</v>
       </c>
@@ -11244,7 +11262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="3:19">
+    <row r="62" customHeight="1" spans="1:22">
       <c r="C62" s="1">
         <v>33208</v>
       </c>
@@ -11276,9 +11294,13 @@
       <c r="S62" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" customFormat="1" customHeight="1" spans="16:16">
+      <c r="V62" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="1:22">
       <c r="P63" s="1"/>
+      <c r="V63" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -497,7 +497,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="318">
   <si>
     <t>_ID</t>
   </si>
@@ -9326,7 +9326,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:V63"/>
+  <dimension ref="A3:U63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -9343,12 +9343,10 @@
     <col min="18" max="18" width="8.91666666666667" style="1" customWidth="1"/>
     <col min="19" max="19" width="13.75" style="1" customWidth="1"/>
     <col min="20" max="20" width="7.375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="1"/>
-    <col min="22" max="22" width="7.875" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -9406,11 +9404,8 @@
       <c r="U3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:22">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
@@ -9468,11 +9463,8 @@
       <c r="U4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:22">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C5" s="2" t="s">
         <v>47</v>
       </c>
@@ -9530,11 +9522,8 @@
       <c r="U5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:22">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C6" s="1">
         <v>31001</v>
       </c>
@@ -9569,7 +9558,7 @@
       <c r="N6" s="1"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C7" s="1">
         <v>31002</v>
       </c>
@@ -9604,7 +9593,7 @@
       <c r="N7" s="1"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C8" s="1">
         <v>31003</v>
       </c>
@@ -9639,7 +9628,7 @@
       <c r="N8" s="1"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C9" s="1">
         <v>31004</v>
       </c>
@@ -9674,7 +9663,7 @@
       <c r="N9" s="1"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C10" s="1">
         <v>31005</v>
       </c>
@@ -9709,7 +9698,7 @@
       <c r="N10" s="1"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C11" s="1">
         <v>31006</v>
       </c>
@@ -9744,7 +9733,7 @@
       <c r="N11" s="1"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C12" s="1">
         <v>31007</v>
       </c>
@@ -9779,7 +9768,7 @@
       <c r="N12" s="1"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C13" s="1">
         <v>31008</v>
       </c>
@@ -9814,7 +9803,7 @@
       <c r="N13" s="1"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C14" s="1">
         <v>31009</v>
       </c>
@@ -9849,7 +9838,7 @@
       <c r="N14" s="1"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C15" s="1">
         <v>31010</v>
       </c>
@@ -9884,7 +9873,7 @@
       <c r="N15" s="1"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C16" s="1">
         <v>31011</v>
       </c>
@@ -9919,7 +9908,7 @@
       <c r="N16" s="1"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" customHeight="1" spans="3:22">
+    <row r="17" customHeight="1" spans="3:19">
       <c r="C17" s="1">
         <v>31012</v>
       </c>
@@ -9952,7 +9941,7 @@
       </c>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C18" s="1">
         <v>31112</v>
       </c>
@@ -9991,7 +9980,7 @@
       </c>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C19" s="1">
         <v>31212</v>
       </c>
@@ -10026,7 +10015,7 @@
       <c r="N19" s="1"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C20" s="1">
         <v>31312</v>
       </c>
@@ -10061,7 +10050,7 @@
       </c>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C21" s="1">
         <v>31108</v>
       </c>
@@ -10092,31 +10081,31 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <v>9</v>
+      </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1">
         <v>2</v>
       </c>
-      <c r="V21" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:22">
+    </row>
+    <row r="22" customHeight="1" spans="3:19">
       <c r="H22" s="3"/>
       <c r="J22" s="3"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" customHeight="1" spans="3:22">
+    <row r="23" customHeight="1" spans="3:19">
       <c r="H23" s="3"/>
       <c r="J23" s="3"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" customHeight="1" spans="3:22">
+    <row r="24" customHeight="1" spans="3:19">
       <c r="H24" s="3"/>
       <c r="J24" s="3"/>
       <c r="P24" s="4"/>
     </row>
-    <row r="25" customHeight="1" spans="3:22">
+    <row r="25" customHeight="1" spans="3:19">
       <c r="C25" s="1">
         <v>32001</v>
       </c>
@@ -10149,7 +10138,7 @@
       </c>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" customHeight="1" spans="3:22">
+    <row r="26" customHeight="1" spans="3:19">
       <c r="C26" s="1">
         <v>32002</v>
       </c>
@@ -10182,7 +10171,7 @@
       </c>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" customHeight="1" spans="3:22">
+    <row r="27" customHeight="1" spans="3:19">
       <c r="C27" s="1">
         <v>32003</v>
       </c>
@@ -10215,7 +10204,7 @@
       </c>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" customHeight="1" spans="3:22">
+    <row r="28" customHeight="1" spans="3:19">
       <c r="C28" s="1">
         <v>32004</v>
       </c>
@@ -10248,7 +10237,7 @@
       </c>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" customHeight="1" spans="3:22">
+    <row r="29" customHeight="1" spans="3:19">
       <c r="C29" s="1">
         <v>32005</v>
       </c>
@@ -10281,7 +10270,7 @@
       </c>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" customHeight="1" spans="3:22">
+    <row r="30" customHeight="1" spans="3:19">
       <c r="C30" s="1">
         <v>32006</v>
       </c>
@@ -10314,7 +10303,7 @@
       </c>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" customHeight="1" spans="3:22">
+    <row r="31" customHeight="1" spans="3:19">
       <c r="C31" s="1">
         <v>32007</v>
       </c>
@@ -10347,7 +10336,7 @@
       </c>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="3:22">
+    <row r="32" customHeight="1" spans="3:19">
       <c r="C32" s="1">
         <v>32008</v>
       </c>
@@ -10380,7 +10369,7 @@
       </c>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" customHeight="1" spans="3:22">
+    <row r="33" customHeight="1" spans="3:20">
       <c r="C33" s="1">
         <v>32009</v>
       </c>
@@ -10413,7 +10402,7 @@
       </c>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" customHeight="1" spans="3:22">
+    <row r="34" customHeight="1" spans="3:20">
       <c r="C34" s="1">
         <v>32010</v>
       </c>
@@ -10446,7 +10435,7 @@
       </c>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" customHeight="1" spans="3:22">
+    <row r="35" customHeight="1" spans="3:20">
       <c r="C35" s="1">
         <v>32011</v>
       </c>
@@ -10479,7 +10468,7 @@
       </c>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" customHeight="1" spans="3:22">
+    <row r="36" customHeight="1" spans="3:20">
       <c r="C36" s="1">
         <v>32012</v>
       </c>
@@ -10512,15 +10501,15 @@
       </c>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" customHeight="1" spans="3:22">
+    <row r="37" customHeight="1" spans="3:20">
       <c r="H37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" customHeight="1" spans="3:22">
+    <row r="38" customHeight="1" spans="3:20">
       <c r="H38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="3:22">
+    <row r="39" customHeight="1" spans="3:20">
       <c r="C39" s="1">
         <v>32102</v>
       </c>
@@ -10556,7 +10545,7 @@
       </c>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" customHeight="1" spans="3:22">
+    <row r="40" customHeight="1" spans="3:20">
       <c r="C40" s="1">
         <v>32202</v>
       </c>
@@ -10589,7 +10578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:22">
+    <row r="41" customHeight="1" spans="3:20">
       <c r="C41" s="1">
         <v>32110</v>
       </c>
@@ -10622,7 +10611,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:22">
+    <row r="42" customHeight="1" spans="3:20">
       <c r="C42" s="1">
         <v>32108</v>
       </c>
@@ -10649,16 +10638,16 @@
       </c>
       <c r="K42" s="1" t="s">
         <v>275</v>
+      </c>
+      <c r="O42" s="1">
+        <v>10</v>
       </c>
       <c r="Q42" s="4"/>
       <c r="S42" s="1">
         <v>2</v>
       </c>
-      <c r="V42" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:22">
+    </row>
+    <row r="43" customHeight="1" spans="3:20">
       <c r="C43" s="1">
         <v>32107</v>
       </c>
@@ -10694,7 +10683,7 @@
       </c>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" customHeight="1" spans="3:22">
+    <row r="44" customHeight="1" spans="3:20">
       <c r="C44" s="1">
         <v>32112</v>
       </c>
@@ -10727,12 +10716,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:22">
+    <row r="45" customHeight="1" spans="3:20">
       <c r="H45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="3:22">
+    <row r="46" customHeight="1" spans="3:20">
       <c r="C46" s="1">
         <v>33001</v>
       </c>
@@ -10765,7 +10754,7 @@
       </c>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" customHeight="1" spans="3:22">
+    <row r="47" customHeight="1" spans="3:20">
       <c r="C47" s="1">
         <v>33002</v>
       </c>
@@ -10798,7 +10787,7 @@
       </c>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" customHeight="1" spans="3:22">
+    <row r="48" customHeight="1" spans="3:20">
       <c r="C48" s="1">
         <v>33003</v>
       </c>
@@ -10831,7 +10820,7 @@
       </c>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" customHeight="1" spans="1:22">
+    <row r="49" customHeight="1" spans="1:20">
       <c r="C49" s="1">
         <v>33004</v>
       </c>
@@ -10864,7 +10853,7 @@
       </c>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" customHeight="1" spans="1:22">
+    <row r="50" customHeight="1" spans="1:20">
       <c r="C50" s="1">
         <v>33005</v>
       </c>
@@ -10897,7 +10886,7 @@
       </c>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" customHeight="1" spans="1:22">
+    <row r="51" customHeight="1" spans="1:20">
       <c r="C51" s="1">
         <v>33006</v>
       </c>
@@ -10930,7 +10919,7 @@
       </c>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" customHeight="1" spans="1:22">
+    <row r="52" customHeight="1" spans="1:20">
       <c r="C52" s="1">
         <v>33007</v>
       </c>
@@ -10963,7 +10952,7 @@
       </c>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" customHeight="1" spans="1:22">
+    <row r="53" customHeight="1" spans="1:20">
       <c r="C53" s="1">
         <v>33008</v>
       </c>
@@ -10996,7 +10985,7 @@
       </c>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" customHeight="1" spans="1:22">
+    <row r="54" customHeight="1" spans="1:20">
       <c r="C54" s="1">
         <v>33009</v>
       </c>
@@ -11029,7 +11018,7 @@
       </c>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" customHeight="1" spans="1:22">
+    <row r="55" customHeight="1" spans="1:20">
       <c r="C55" s="1">
         <v>33010</v>
       </c>
@@ -11062,7 +11051,7 @@
       </c>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" customHeight="1" spans="1:22">
+    <row r="56" customHeight="1" spans="1:20">
       <c r="C56" s="1">
         <v>33011</v>
       </c>
@@ -11095,7 +11084,7 @@
       </c>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" customHeight="1" spans="1:22">
+    <row r="57" customHeight="1" spans="1:20">
       <c r="C57" s="1">
         <v>33012</v>
       </c>
@@ -11128,7 +11117,7 @@
       </c>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="1:22">
+    <row r="58" customFormat="1" customHeight="1" spans="1:20">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -11143,9 +11132,8 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-      <c r="V58" s="1"/>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:22">
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A59" s="1" t="s">
         <v>310</v>
       </c>
@@ -11190,7 +11178,7 @@
       </c>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:22">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="C60" s="1">
         <v>33212</v>
       </c>
@@ -11229,7 +11217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:22">
+    <row r="61" customHeight="1" spans="1:20">
       <c r="C61" s="1">
         <v>33108</v>
       </c>
@@ -11262,7 +11250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:22">
+    <row r="62" customHeight="1" spans="1:20">
       <c r="C62" s="1">
         <v>33208</v>
       </c>
@@ -11289,18 +11277,17 @@
       </c>
       <c r="K62" s="1" t="s">
         <v>275</v>
+      </c>
+      <c r="O62" s="1">
+        <v>8</v>
       </c>
       <c r="Q62" s="4"/>
       <c r="S62" s="1">
         <v>2</v>
       </c>
-      <c r="V62" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" customHeight="1" spans="1:22">
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="1:20">
       <c r="P63" s="1"/>
-      <c r="V63" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -497,7 +497,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="292">
   <si>
     <t>_ID</t>
   </si>
@@ -1264,193 +1264,115 @@
     <t>Miss</t>
   </si>
   <si>
-    <t>基础剑术·通神</t>
-  </si>
-  <si>
-    <t>流光剑法·通神</t>
-  </si>
-  <si>
-    <t>旋风斩·通神</t>
-  </si>
-  <si>
-    <t>腾空斩·通神</t>
-  </si>
-  <si>
-    <t>武神盾·通神</t>
-  </si>
-  <si>
-    <t>武力精通·通神</t>
-  </si>
-  <si>
-    <t>烈焰斩·通神</t>
-  </si>
-  <si>
-    <t>战吼·通神</t>
-  </si>
-  <si>
-    <t>裂天斩·通神</t>
-  </si>
-  <si>
-    <t>裂地斩·通神</t>
-  </si>
-  <si>
-    <t>战士之魂·通神</t>
-  </si>
-  <si>
-    <t>剑二十三·通神</t>
+    <t>基础剑术·入圣</t>
+  </si>
+  <si>
+    <t>流光剑法·入圣</t>
+  </si>
+  <si>
+    <t>旋风斩·入圣</t>
+  </si>
+  <si>
+    <t>腾空斩·入圣</t>
+  </si>
+  <si>
+    <t>武神盾·入圣</t>
+  </si>
+  <si>
+    <t>武力精通·入圣</t>
+  </si>
+  <si>
+    <t>烈焰斩·入圣</t>
+  </si>
+  <si>
+    <t>战吼·入圣</t>
+  </si>
+  <si>
+    <t>裂天斩·入圣</t>
+  </si>
+  <si>
+    <t>裂地斩·入圣</t>
+  </si>
+  <si>
+    <t>战士之魂·入圣</t>
+  </si>
+  <si>
+    <t>剑二十三·入圣</t>
   </si>
   <si>
     <t>提高此技能系数30%系数增幅</t>
   </si>
   <si>
-    <t>剑二十三·吸血</t>
-  </si>
-  <si>
-    <t>附带10%吸血效果</t>
-  </si>
-  <si>
-    <t>剑二十三·祝福</t>
-  </si>
-  <si>
-    <t>技能提高20%攻击</t>
-  </si>
-  <si>
-    <t>剑二十三·致命</t>
-  </si>
-  <si>
-    <t>技能提高20%最终伤害</t>
-  </si>
-  <si>
-    <t>战吼·破限</t>
-  </si>
-  <si>
-    <t>额外增加2次叠加上限</t>
-  </si>
-  <si>
-    <t>火球术·通神</t>
-  </si>
-  <si>
-    <t>落雷术·通神</t>
-  </si>
-  <si>
-    <t>火焰墙·通神</t>
-  </si>
-  <si>
-    <t>烈焰环·通神</t>
-  </si>
-  <si>
-    <t>法力盾·通神</t>
-  </si>
-  <si>
-    <t>法术精通·通神</t>
-  </si>
-  <si>
-    <t>冰爆术·通神</t>
-  </si>
-  <si>
-    <t>心灵传送·通神</t>
-  </si>
-  <si>
-    <t>毁灭流星·通神</t>
-  </si>
-  <si>
-    <t>分身术·通神</t>
-  </si>
-  <si>
-    <t>法师之魂·通神</t>
-  </si>
-  <si>
-    <t>魔尊附体·通神</t>
-  </si>
-  <si>
-    <t>落雷术·吸血</t>
-  </si>
-  <si>
-    <t>落雷术·神术</t>
-  </si>
-  <si>
-    <t>额外再多一个攻击目标</t>
-  </si>
-  <si>
-    <t>分身术·超持久</t>
-  </si>
-  <si>
-    <t>再增加60秒持续时间</t>
-  </si>
-  <si>
-    <t>心灵传送·破限</t>
-  </si>
-  <si>
-    <t>冰爆术·哀霜Ⅱ</t>
-  </si>
-  <si>
-    <t>使敌人受到的伤害增加20%，持续5秒</t>
-  </si>
-  <si>
-    <t>魔尊附体·双倍</t>
-  </si>
-  <si>
-    <t>每次施法,额外获取一次加成,不能突破加成上限</t>
-  </si>
-  <si>
-    <t>疗伤术·通神</t>
-  </si>
-  <si>
-    <t>驱魔符·通神</t>
-  </si>
-  <si>
-    <t>毒咒术·通神</t>
-  </si>
-  <si>
-    <t>召唤小兵·通神</t>
-  </si>
-  <si>
-    <t>道力盾·通神</t>
-  </si>
-  <si>
-    <t>道力精通·通神</t>
-  </si>
-  <si>
-    <t>召唤魔兽·通神</t>
-  </si>
-  <si>
-    <t>隐身道法·通神</t>
-  </si>
-  <si>
-    <t>召唤月神·通神</t>
-  </si>
-  <si>
-    <t>无极道体·通神</t>
-  </si>
-  <si>
-    <t>道士之魂·通神</t>
-  </si>
-  <si>
-    <t>召唤白虎·通神</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>召唤白虎·吸血</t>
-  </si>
-  <si>
-    <t>附带15%吸血效果</t>
-  </si>
-  <si>
-    <t>召唤白虎·复制</t>
-  </si>
-  <si>
-    <t>多召唤一只白虎</t>
-  </si>
-  <si>
-    <t>隐身道法·神术</t>
-  </si>
-  <si>
-    <t>再额外增加1秒持续时间</t>
-  </si>
-  <si>
-    <t>隐身道法·破限</t>
+    <t>火球术·入圣</t>
+  </si>
+  <si>
+    <t>落雷术·入圣</t>
+  </si>
+  <si>
+    <t>火焰墙·入圣</t>
+  </si>
+  <si>
+    <t>烈焰环·入圣</t>
+  </si>
+  <si>
+    <t>法力盾·入圣</t>
+  </si>
+  <si>
+    <t>法术精通·入圣</t>
+  </si>
+  <si>
+    <t>冰爆术·入圣</t>
+  </si>
+  <si>
+    <t>心灵传送·入圣</t>
+  </si>
+  <si>
+    <t>毁灭流星·入圣</t>
+  </si>
+  <si>
+    <t>分身术·入圣</t>
+  </si>
+  <si>
+    <t>法师之魂·入圣</t>
+  </si>
+  <si>
+    <t>魔尊附体·入圣</t>
+  </si>
+  <si>
+    <t>疗伤术·入圣</t>
+  </si>
+  <si>
+    <t>驱魔符·入圣</t>
+  </si>
+  <si>
+    <t>毒咒术·入圣</t>
+  </si>
+  <si>
+    <t>召唤小兵·入圣</t>
+  </si>
+  <si>
+    <t>道力盾·入圣</t>
+  </si>
+  <si>
+    <t>道力精通·入圣</t>
+  </si>
+  <si>
+    <t>召唤魔兽·入圣</t>
+  </si>
+  <si>
+    <t>隐身道法·入圣</t>
+  </si>
+  <si>
+    <t>召唤月神·入圣</t>
+  </si>
+  <si>
+    <t>无极道体·入圣</t>
+  </si>
+  <si>
+    <t>道士之魂·入圣</t>
+  </si>
+  <si>
+    <t>召唤白虎·入圣</t>
   </si>
 </sst>
 </file>
@@ -9326,7 +9248,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:U63"/>
+  <dimension ref="C3:U63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -9525,10 +9447,10 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C6" s="1">
-        <v>31001</v>
+        <v>41001</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1">
         <v>300</v>
@@ -9560,10 +9482,10 @@
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C7" s="1">
-        <v>31002</v>
+        <v>41002</v>
       </c>
       <c r="D7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -9595,10 +9517,10 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C8" s="1">
-        <v>31003</v>
+        <v>41003</v>
       </c>
       <c r="D8" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="1">
         <v>300</v>
@@ -9630,10 +9552,10 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C9" s="1">
-        <v>31004</v>
+        <v>41004</v>
       </c>
       <c r="D9" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="1">
         <v>300</v>
@@ -9665,10 +9587,10 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C10" s="1">
-        <v>31005</v>
+        <v>41005</v>
       </c>
       <c r="D10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="1">
         <v>100</v>
@@ -9700,10 +9622,10 @@
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C11" s="1">
-        <v>31006</v>
+        <v>41006</v>
       </c>
       <c r="D11" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -9735,10 +9657,10 @@
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C12" s="1">
-        <v>31007</v>
+        <v>41007</v>
       </c>
       <c r="D12" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1">
         <v>300</v>
@@ -9770,10 +9692,10 @@
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C13" s="1">
-        <v>31008</v>
+        <v>41008</v>
       </c>
       <c r="D13" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
@@ -9805,10 +9727,10 @@
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C14" s="1">
-        <v>31009</v>
+        <v>41009</v>
       </c>
       <c r="D14" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1">
         <v>300</v>
@@ -9840,10 +9762,10 @@
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C15" s="1">
-        <v>31010</v>
+        <v>41010</v>
       </c>
       <c r="D15" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -9875,10 +9797,10 @@
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C16" s="1">
-        <v>31011</v>
+        <v>41011</v>
       </c>
       <c r="D16" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="1">
         <v>10</v>
@@ -9908,12 +9830,12 @@
       <c r="N16" s="1"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" customHeight="1" spans="3:19">
+    <row r="17" customHeight="1" spans="3:17">
       <c r="C17" s="1">
-        <v>31012</v>
+        <v>41012</v>
       </c>
       <c r="D17" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="1">
         <v>10</v>
@@ -9941,176 +9863,70 @@
       </c>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C18" s="1">
-        <v>31112</v>
-      </c>
-      <c r="D18" s="1">
-        <v>5</v>
-      </c>
-      <c r="E18" s="1">
-        <v>10</v>
-      </c>
-      <c r="F18" s="1">
-        <v>5</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1012</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>269</v>
-      </c>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="H18" s="3"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="4"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="1">
-        <v>101</v>
-      </c>
-      <c r="P18" s="1">
-        <v>10</v>
-      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C19" s="1">
-        <v>31212</v>
-      </c>
-      <c r="D19" s="1">
-        <v>5</v>
-      </c>
-      <c r="E19" s="1">
-        <v>10</v>
-      </c>
-      <c r="F19" s="1">
-        <v>5</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1012</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>271</v>
-      </c>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="H19" s="3"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="1">
-        <v>20</v>
-      </c>
+      <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C20" s="1">
-        <v>31312</v>
-      </c>
-      <c r="D20" s="1">
-        <v>5</v>
-      </c>
-      <c r="E20" s="1">
-        <v>10</v>
-      </c>
-      <c r="F20" s="1">
-        <v>5</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1012</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>273</v>
-      </c>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="H20" s="3"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1">
-        <v>20</v>
-      </c>
+      <c r="N20" s="1"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C21" s="1">
-        <v>31108</v>
-      </c>
-      <c r="D21" s="1">
-        <v>5</v>
-      </c>
-      <c r="E21" s="1">
-        <v>50</v>
-      </c>
-      <c r="F21" s="1">
-        <v>20</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1008</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>275</v>
-      </c>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="H21" s="3"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-      <c r="O21" s="1">
-        <v>9</v>
-      </c>
+      <c r="O21" s="1"/>
       <c r="Q21" s="4"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:19">
+    </row>
+    <row r="22" customHeight="1" spans="3:17">
       <c r="H22" s="3"/>
       <c r="J22" s="3"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" customHeight="1" spans="3:19">
+    <row r="23" customHeight="1" spans="3:17">
       <c r="H23" s="3"/>
       <c r="J23" s="3"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" customHeight="1" spans="3:19">
+    <row r="24" customHeight="1" spans="3:17">
       <c r="H24" s="3"/>
       <c r="J24" s="3"/>
       <c r="P24" s="4"/>
     </row>
-    <row r="25" customHeight="1" spans="3:19">
+    <row r="25" customHeight="1" spans="3:17">
       <c r="C25" s="1">
-        <v>32001</v>
+        <v>42001</v>
       </c>
       <c r="D25" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="1">
         <v>300</v>
@@ -10128,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>193</v>
@@ -10138,12 +9954,12 @@
       </c>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" customHeight="1" spans="3:19">
+    <row r="26" customHeight="1" spans="3:17">
       <c r="C26" s="1">
-        <v>32002</v>
+        <v>42002</v>
       </c>
       <c r="D26" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
@@ -10161,7 +9977,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>193</v>
@@ -10171,12 +9987,12 @@
       </c>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" customHeight="1" spans="3:19">
+    <row r="27" customHeight="1" spans="3:17">
       <c r="C27" s="1">
-        <v>32003</v>
+        <v>42003</v>
       </c>
       <c r="D27" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="1">
         <v>300</v>
@@ -10194,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>193</v>
@@ -10204,12 +10020,12 @@
       </c>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" customHeight="1" spans="3:19">
+    <row r="28" customHeight="1" spans="3:17">
       <c r="C28" s="1">
-        <v>32004</v>
+        <v>42004</v>
       </c>
       <c r="D28" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" s="1">
         <v>300</v>
@@ -10227,7 +10043,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>193</v>
@@ -10237,12 +10053,12 @@
       </c>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" customHeight="1" spans="3:19">
+    <row r="29" customHeight="1" spans="3:17">
       <c r="C29" s="1">
-        <v>32005</v>
+        <v>42005</v>
       </c>
       <c r="D29" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" s="1">
         <v>100</v>
@@ -10260,7 +10076,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>193</v>
@@ -10270,12 +10086,12 @@
       </c>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" customHeight="1" spans="3:19">
+    <row r="30" customHeight="1" spans="3:17">
       <c r="C30" s="1">
-        <v>32006</v>
+        <v>42006</v>
       </c>
       <c r="D30" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" s="1">
         <v>50</v>
@@ -10293,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
@@ -10303,12 +10119,12 @@
       </c>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" customHeight="1" spans="3:19">
+    <row r="31" customHeight="1" spans="3:17">
       <c r="C31" s="1">
-        <v>32007</v>
+        <v>42007</v>
       </c>
       <c r="D31" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="1">
         <v>300</v>
@@ -10326,7 +10142,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>193</v>
@@ -10336,12 +10152,12 @@
       </c>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="3:19">
+    <row r="32" customHeight="1" spans="3:17">
       <c r="C32" s="1">
-        <v>32008</v>
+        <v>42008</v>
       </c>
       <c r="D32" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" s="1">
         <v>50</v>
@@ -10359,7 +10175,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>193</v>
@@ -10369,12 +10185,12 @@
       </c>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" customHeight="1" spans="3:20">
+    <row r="33" customHeight="1" spans="3:17">
       <c r="C33" s="1">
-        <v>32009</v>
+        <v>42009</v>
       </c>
       <c r="D33" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="1">
         <v>300</v>
@@ -10392,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>193</v>
@@ -10402,12 +10218,12 @@
       </c>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" customHeight="1" spans="3:20">
+    <row r="34" customHeight="1" spans="3:17">
       <c r="C34" s="1">
-        <v>32010</v>
+        <v>42010</v>
       </c>
       <c r="D34" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="1">
         <v>10</v>
@@ -10425,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>193</v>
@@ -10435,12 +10251,12 @@
       </c>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" customHeight="1" spans="3:20">
+    <row r="35" customHeight="1" spans="3:17">
       <c r="C35" s="1">
-        <v>32011</v>
+        <v>42011</v>
       </c>
       <c r="D35" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="1">
         <v>10</v>
@@ -10458,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>193</v>
@@ -10468,12 +10284,12 @@
       </c>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" customHeight="1" spans="3:20">
+    <row r="36" customHeight="1" spans="3:17">
       <c r="C36" s="1">
-        <v>32012</v>
+        <v>42012</v>
       </c>
       <c r="D36" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="1">
         <v>10</v>
@@ -10491,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>267</v>
@@ -10501,232 +10317,67 @@
       </c>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" customHeight="1" spans="3:20">
+    <row r="37" customHeight="1" spans="3:17">
       <c r="H37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" customHeight="1" spans="3:20">
+    <row r="38" customHeight="1" spans="3:17">
       <c r="H38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="3:20">
-      <c r="C39" s="1">
-        <v>32102</v>
-      </c>
-      <c r="D39" s="1">
-        <v>5</v>
-      </c>
-      <c r="E39" s="1">
-        <v>10</v>
-      </c>
-      <c r="F39" s="1">
-        <v>5</v>
-      </c>
-      <c r="G39" s="1">
-        <v>2</v>
-      </c>
-      <c r="H39" s="3">
-        <v>2002</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="O39" s="1">
-        <v>101</v>
-      </c>
-      <c r="P39" s="1">
-        <v>10</v>
-      </c>
+    <row r="39" customHeight="1" spans="3:17">
+      <c r="H39" s="3"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" customHeight="1" spans="3:20">
-      <c r="C40" s="1">
-        <v>32202</v>
-      </c>
-      <c r="D40" s="1">
-        <v>5</v>
-      </c>
-      <c r="E40" s="1">
-        <v>10</v>
-      </c>
-      <c r="F40" s="1">
-        <v>5</v>
-      </c>
-      <c r="G40" s="1">
-        <v>2</v>
-      </c>
-      <c r="H40" s="3">
-        <v>2002</v>
-      </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>290</v>
-      </c>
+    <row r="40" customHeight="1" spans="3:17">
+      <c r="H40" s="3"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="4"/>
       <c r="Q40" s="4"/>
-      <c r="S40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:20">
-      <c r="C41" s="1">
-        <v>32110</v>
-      </c>
-      <c r="D41" s="1">
-        <v>5</v>
-      </c>
-      <c r="E41" s="1">
-        <v>10</v>
-      </c>
-      <c r="F41" s="1">
-        <v>5</v>
-      </c>
-      <c r="G41" s="1">
-        <v>2</v>
-      </c>
-      <c r="H41" s="3">
-        <v>2010</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>292</v>
-      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:17">
+      <c r="H41" s="3"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="1"/>
       <c r="Q41" s="4"/>
-      <c r="T41" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:20">
-      <c r="C42" s="1">
-        <v>32108</v>
-      </c>
-      <c r="D42" s="1">
-        <v>5</v>
-      </c>
-      <c r="E42" s="1">
-        <v>10</v>
-      </c>
-      <c r="F42" s="1">
-        <v>5</v>
-      </c>
-      <c r="G42" s="1">
-        <v>2</v>
-      </c>
-      <c r="H42" s="3">
-        <v>2008</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="O42" s="1">
-        <v>10</v>
-      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:17">
+      <c r="H42" s="3"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="1"/>
       <c r="Q42" s="4"/>
-      <c r="S42" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:20">
-      <c r="C43" s="1">
-        <v>32107</v>
-      </c>
-      <c r="D43" s="1">
-        <v>5</v>
-      </c>
-      <c r="E43" s="1">
-        <v>10</v>
-      </c>
-      <c r="F43" s="1">
-        <v>5</v>
-      </c>
-      <c r="G43" s="1">
-        <v>2</v>
-      </c>
-      <c r="H43" s="3">
-        <v>2007</v>
-      </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="O43" s="1">
-        <v>17</v>
-      </c>
-      <c r="P43" s="1">
-        <v>30</v>
-      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:17">
+      <c r="H43" s="3"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="1"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" customHeight="1" spans="3:20">
-      <c r="C44" s="1">
-        <v>32112</v>
-      </c>
-      <c r="D44" s="1">
-        <v>5</v>
-      </c>
-      <c r="E44" s="1">
-        <v>10</v>
-      </c>
-      <c r="F44" s="1">
-        <v>5</v>
-      </c>
-      <c r="G44" s="1">
-        <v>2</v>
-      </c>
-      <c r="H44" s="3">
-        <v>2012</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>297</v>
-      </c>
+    <row r="44" customHeight="1" spans="3:17">
+      <c r="H44" s="3"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="1"/>
       <c r="Q44" s="4"/>
-      <c r="S44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:20">
+    </row>
+    <row r="45" customHeight="1" spans="3:17">
       <c r="H45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="3:20">
+    <row r="46" customHeight="1" spans="3:17">
       <c r="C46" s="1">
-        <v>33001</v>
+        <v>43001</v>
       </c>
       <c r="D46" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" s="1">
         <v>300</v>
@@ -10744,7 +10395,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>193</v>
@@ -10754,12 +10405,12 @@
       </c>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" customHeight="1" spans="3:20">
+    <row r="47" customHeight="1" spans="3:17">
       <c r="C47" s="1">
-        <v>33002</v>
+        <v>43002</v>
       </c>
       <c r="D47" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E47" s="1">
         <v>50</v>
@@ -10777,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>193</v>
@@ -10787,12 +10438,12 @@
       </c>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" customHeight="1" spans="3:20">
+    <row r="48" customHeight="1" spans="3:17">
       <c r="C48" s="1">
-        <v>33003</v>
+        <v>43003</v>
       </c>
       <c r="D48" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" s="1">
         <v>300</v>
@@ -10810,7 +10461,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>193</v>
@@ -10820,12 +10471,12 @@
       </c>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" customHeight="1" spans="1:20">
+    <row r="49" customHeight="1" spans="3:17">
       <c r="C49" s="1">
-        <v>33004</v>
+        <v>43004</v>
       </c>
       <c r="D49" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E49" s="1">
         <v>300</v>
@@ -10843,7 +10494,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>193</v>
@@ -10853,12 +10504,12 @@
       </c>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" customHeight="1" spans="1:20">
+    <row r="50" customHeight="1" spans="3:17">
       <c r="C50" s="1">
-        <v>33005</v>
+        <v>43005</v>
       </c>
       <c r="D50" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E50" s="1">
         <v>100</v>
@@ -10876,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>193</v>
@@ -10886,12 +10537,12 @@
       </c>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" customHeight="1" spans="1:20">
+    <row r="51" customHeight="1" spans="3:17">
       <c r="C51" s="1">
-        <v>33006</v>
+        <v>43006</v>
       </c>
       <c r="D51" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51" s="1">
         <v>50</v>
@@ -10909,7 +10560,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>193</v>
@@ -10919,12 +10570,12 @@
       </c>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" customHeight="1" spans="1:20">
+    <row r="52" customHeight="1" spans="3:17">
       <c r="C52" s="1">
-        <v>33007</v>
+        <v>43007</v>
       </c>
       <c r="D52" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E52" s="1">
         <v>300</v>
@@ -10942,7 +10593,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>193</v>
@@ -10952,12 +10603,12 @@
       </c>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" customHeight="1" spans="1:20">
+    <row r="53" customHeight="1" spans="3:17">
       <c r="C53" s="1">
-        <v>33008</v>
+        <v>43008</v>
       </c>
       <c r="D53" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" s="1">
         <v>50</v>
@@ -10975,7 +10626,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>193</v>
@@ -10985,12 +10636,12 @@
       </c>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" customHeight="1" spans="1:20">
+    <row r="54" customHeight="1" spans="3:17">
       <c r="C54" s="1">
-        <v>33009</v>
+        <v>43009</v>
       </c>
       <c r="D54" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E54" s="1">
         <v>300</v>
@@ -11008,7 +10659,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>193</v>
@@ -11018,12 +10669,12 @@
       </c>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" customHeight="1" spans="1:20">
+    <row r="55" customHeight="1" spans="3:17">
       <c r="C55" s="1">
-        <v>33010</v>
+        <v>43010</v>
       </c>
       <c r="D55" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E55" s="1">
         <v>10</v>
@@ -11041,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>193</v>
@@ -11051,12 +10702,12 @@
       </c>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" customHeight="1" spans="1:20">
+    <row r="56" customHeight="1" spans="3:17">
       <c r="C56" s="1">
-        <v>33011</v>
+        <v>43011</v>
       </c>
       <c r="D56" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56" s="1">
         <v>10</v>
@@ -11074,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>193</v>
@@ -11084,12 +10735,12 @@
       </c>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" customHeight="1" spans="1:20">
+    <row r="57" customHeight="1" spans="3:17">
       <c r="C57" s="1">
-        <v>33012</v>
+        <v>43012</v>
       </c>
       <c r="D57" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" s="1">
         <v>10</v>
@@ -11107,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>267</v>
@@ -11117,7 +10768,7 @@
       </c>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="1:20">
+    <row r="58" customFormat="1" customHeight="1" spans="3:17">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -11133,160 +10784,38 @@
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A59" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C59" s="1">
-        <v>33112</v>
-      </c>
-      <c r="D59" s="1">
-        <v>5</v>
-      </c>
-      <c r="E59" s="1">
-        <v>10</v>
-      </c>
-      <c r="F59" s="1">
-        <v>5</v>
-      </c>
-      <c r="G59" s="1">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3012</v>
-      </c>
-      <c r="I59" s="1">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>312</v>
-      </c>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="H59" s="3"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="4"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
-      <c r="O59" s="1">
-        <v>101</v>
-      </c>
-      <c r="P59" s="1">
-        <v>15</v>
-      </c>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="C60" s="1">
-        <v>33212</v>
-      </c>
-      <c r="D60" s="1">
-        <v>5</v>
-      </c>
-      <c r="E60" s="1">
-        <v>10</v>
-      </c>
-      <c r="F60" s="1">
-        <v>10</v>
-      </c>
-      <c r="G60" s="1">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3">
-        <v>3012</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:20">
-      <c r="C61" s="1">
-        <v>33108</v>
-      </c>
-      <c r="D61" s="1">
-        <v>5</v>
-      </c>
-      <c r="E61" s="1">
-        <v>10</v>
-      </c>
-      <c r="F61" s="1">
-        <v>5</v>
-      </c>
-      <c r="G61" s="1">
-        <v>3</v>
-      </c>
-      <c r="H61" s="3">
-        <v>3008</v>
-      </c>
-      <c r="I61" s="1">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>316</v>
-      </c>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="H60" s="3"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" customHeight="1" spans="3:17">
+      <c r="H61" s="3"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="1"/>
       <c r="Q61" s="4"/>
-      <c r="T61" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:20">
-      <c r="C62" s="1">
-        <v>33208</v>
-      </c>
-      <c r="D62" s="1">
-        <v>5</v>
-      </c>
-      <c r="E62" s="1">
-        <v>10</v>
-      </c>
-      <c r="F62" s="1">
-        <v>5</v>
-      </c>
-      <c r="G62" s="1">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3008</v>
-      </c>
-      <c r="I62" s="1">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="O62" s="1">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:17">
+      <c r="H62" s="3"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="1"/>
       <c r="Q62" s="4"/>
-      <c r="S62" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" customHeight="1" spans="1:20">
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="3:17">
       <c r="P63" s="1"/>
     </row>
   </sheetData>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -554,7 +554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="368">
   <si>
     <t>_ID</t>
   </si>
@@ -1511,6 +1511,9 @@
   </si>
   <si>
     <t>基础剑术·入圣</t>
+  </si>
+  <si>
+    <t>提高此技能系数75%系数增幅</t>
   </si>
   <si>
     <t>流光剑法·入圣</t>
@@ -1839,12 +1842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2304,7 +2307,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2313,8 +2316,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6765,1436 +6766,1434 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6">
+    <row r="6" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
         <v>1001</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
         <v>20</v>
       </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
-        <v>0</v>
-      </c>
-      <c r="W6" s="6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6">
+      <c r="S6" s="4">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4">
         <v>101</v>
       </c>
     </row>
-    <row r="7" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C7" s="6">
+    <row r="7" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4">
         <v>2001</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6">
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4">
         <v>4</v>
       </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
         <v>100</v>
       </c>
-      <c r="S7" s="6">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6">
-        <v>0</v>
-      </c>
-      <c r="V7" s="6">
-        <v>0</v>
-      </c>
-      <c r="W7" s="6">
-        <v>0</v>
-      </c>
-      <c r="X7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="6">
+      <c r="S7" s="4">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4">
         <v>103</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C8" s="6">
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C8" s="4">
         <v>3</v>
       </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6">
-        <v>1</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
         <v>3001</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6">
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4">
         <v>4</v>
       </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
         <v>100</v>
       </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>0</v>
-      </c>
-      <c r="W8" s="6">
-        <v>0</v>
-      </c>
-      <c r="X8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="6">
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4">
         <v>102</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C9" s="6">
+    <row r="9" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C9" s="4">
         <v>4</v>
       </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
         <v>3002</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6">
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4">
         <v>4</v>
       </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6">
-        <v>50</v>
-      </c>
-      <c r="S9" s="6">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6">
-        <v>0</v>
-      </c>
-      <c r="U9" s="6">
-        <v>0</v>
-      </c>
-      <c r="V9" s="6">
-        <v>0</v>
-      </c>
-      <c r="W9" s="6">
-        <v>0</v>
-      </c>
-      <c r="X9" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="6">
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4">
+        <v>50</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4">
+        <v>0</v>
+      </c>
+      <c r="X9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="4">
         <v>104</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C10" s="6">
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C10" s="4">
         <v>5</v>
       </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1</v>
-      </c>
-      <c r="F10" s="6">
-        <v>1</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
         <v>1001</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6">
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4">
         <v>4</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="4">
         <v>3</v>
       </c>
-      <c r="P10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>50</v>
-      </c>
-      <c r="S10" s="6">
-        <v>0</v>
-      </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
-        <v>0</v>
-      </c>
-      <c r="V10" s="6">
-        <v>0</v>
-      </c>
-      <c r="W10" s="6">
-        <v>0</v>
-      </c>
-      <c r="X10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="6">
+      <c r="P10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4">
+        <v>50</v>
+      </c>
+      <c r="S10" s="4">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4">
+        <v>0</v>
+      </c>
+      <c r="X10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="4">
         <v>107</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C11" s="6">
+    <row r="11" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C11" s="4">
         <v>6</v>
       </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7">
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4">
         <v>2007</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="J11" s="6">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="7">
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4">
         <v>2</v>
       </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6">
-        <v>0</v>
-      </c>
-      <c r="V11" s="6">
-        <v>0</v>
-      </c>
-      <c r="W11" s="6">
-        <v>0</v>
-      </c>
-      <c r="X11" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="6">
+      <c r="O11" s="4">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4">
+        <v>0</v>
+      </c>
+      <c r="W11" s="4">
+        <v>0</v>
+      </c>
+      <c r="X11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="4">
         <v>305</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C12" s="6">
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C12" s="4">
         <v>7</v>
       </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
         <v>1006</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6">
-        <v>0</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <v>50</v>
-      </c>
-      <c r="S12" s="6">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6">
-        <v>0</v>
-      </c>
-      <c r="V12" s="6">
-        <v>0</v>
-      </c>
-      <c r="W12" s="6">
-        <v>0</v>
-      </c>
-      <c r="X12" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C13" s="6">
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4">
+        <v>50</v>
+      </c>
+      <c r="S12" s="4">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
+        <v>0</v>
+      </c>
+      <c r="W12" s="4">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C13" s="4">
         <v>8</v>
       </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6">
-        <v>1</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
         <v>2006</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="J13" s="6">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6">
-        <v>0</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6">
-        <v>50</v>
-      </c>
-      <c r="S13" s="6">
-        <v>0</v>
-      </c>
-      <c r="T13" s="6">
-        <v>0</v>
-      </c>
-      <c r="U13" s="6">
-        <v>0</v>
-      </c>
-      <c r="V13" s="6">
-        <v>0</v>
-      </c>
-      <c r="W13" s="6">
-        <v>0</v>
-      </c>
-      <c r="X13" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C14" s="6">
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
+        <v>50</v>
+      </c>
+      <c r="S13" s="4">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
+        <v>0</v>
+      </c>
+      <c r="W13" s="4">
+        <v>0</v>
+      </c>
+      <c r="X13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C14" s="4">
         <v>9</v>
       </c>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1</v>
-      </c>
-      <c r="F14" s="6">
-        <v>1</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
         <v>3006</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="J14" s="6">
-        <v>0</v>
-      </c>
-      <c r="K14" s="6">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6">
-        <v>0</v>
-      </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6">
-        <v>0</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6">
-        <v>50</v>
-      </c>
-      <c r="S14" s="6">
-        <v>0</v>
-      </c>
-      <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="6">
-        <v>0</v>
-      </c>
-      <c r="V14" s="6">
-        <v>0</v>
-      </c>
-      <c r="W14" s="6">
-        <v>0</v>
-      </c>
-      <c r="X14" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C15" s="6">
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>50</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
+        <v>0</v>
+      </c>
+      <c r="W14" s="4">
+        <v>0</v>
+      </c>
+      <c r="X14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C15" s="4">
         <v>10</v>
       </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4">
         <v>1002</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="J15" s="6">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
         <v>20</v>
       </c>
-      <c r="S15" s="6">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6">
-        <v>0</v>
-      </c>
-      <c r="V15" s="6">
-        <v>0</v>
-      </c>
-      <c r="W15" s="6">
-        <v>0</v>
-      </c>
-      <c r="X15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="6">
+      <c r="S15" s="4">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="4">
         <v>101</v>
       </c>
     </row>
-    <row r="16" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C16" s="6">
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C16" s="4">
         <v>11</v>
       </c>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4">
         <v>2007</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="J16" s="7">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6">
-        <v>0</v>
-      </c>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6">
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4">
         <v>5</v>
       </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
         <v>30</v>
       </c>
-      <c r="S16" s="6">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6">
-        <v>0</v>
-      </c>
-      <c r="V16" s="6">
-        <v>0</v>
-      </c>
-      <c r="W16" s="6">
-        <v>0</v>
-      </c>
-      <c r="X16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="6">
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="17" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C17" s="6">
+    <row r="17" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C17" s="4">
         <v>12</v>
       </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7">
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4">
         <v>1007</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="J17" s="7">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6">
-        <v>0</v>
-      </c>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6">
-        <v>0</v>
-      </c>
-      <c r="O17" s="6">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6">
-        <v>0</v>
-      </c>
-      <c r="U17" s="6">
-        <v>0</v>
-      </c>
-      <c r="V17" s="6">
-        <v>0</v>
-      </c>
-      <c r="W17" s="6">
-        <v>0</v>
-      </c>
-      <c r="X17" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="6">
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
+        <v>0</v>
+      </c>
+      <c r="W17" s="4">
+        <v>0</v>
+      </c>
+      <c r="X17" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="4">
         <v>500</v>
       </c>
     </row>
-    <row r="18" s="6" customFormat="1" ht="17" customHeight="1" spans="3:27">
-      <c r="C18" s="6">
+    <row r="18" s="4" customFormat="1" ht="17" customHeight="1" spans="3:27">
+      <c r="C18" s="4">
         <v>13</v>
       </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7">
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4">
         <v>1008</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="J18" s="7">
-        <v>0</v>
-      </c>
-      <c r="K18" s="6">
-        <v>0</v>
-      </c>
-      <c r="L18" s="6">
-        <v>0</v>
-      </c>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6">
-        <v>0</v>
-      </c>
-      <c r="O18" s="6">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <v>1</v>
-      </c>
-      <c r="S18" s="6">
-        <v>0</v>
-      </c>
-      <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="6">
-        <v>0</v>
-      </c>
-      <c r="V18" s="6">
-        <v>0</v>
-      </c>
-      <c r="W18" s="6">
-        <v>0</v>
-      </c>
-      <c r="X18" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="6">
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4">
+        <v>1</v>
+      </c>
+      <c r="S18" s="4">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
+        <v>0</v>
+      </c>
+      <c r="W18" s="4">
+        <v>0</v>
+      </c>
+      <c r="X18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="19" s="6" customFormat="1" ht="17" customHeight="1" spans="3:27">
-      <c r="C19" s="6">
+    <row r="19" s="4" customFormat="1" ht="17" customHeight="1" spans="3:27">
+      <c r="C19" s="4">
         <v>14</v>
       </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1</v>
-      </c>
-      <c r="F19" s="6">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7">
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4">
         <v>2008</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="J19" s="7">
-        <v>0</v>
-      </c>
-      <c r="K19" s="6">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6">
-        <v>0</v>
-      </c>
-      <c r="O19" s="6">
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
         <v>3</v>
       </c>
-      <c r="P19" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6">
-        <v>0</v>
-      </c>
-      <c r="U19" s="6">
-        <v>0</v>
-      </c>
-      <c r="V19" s="6">
-        <v>0</v>
-      </c>
-      <c r="W19" s="6">
-        <v>0</v>
-      </c>
-      <c r="X19" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="6">
+      <c r="P19" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0</v>
+      </c>
+      <c r="W19" s="4">
+        <v>0</v>
+      </c>
+      <c r="X19" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="20" s="6" customFormat="1" ht="17" customHeight="1" spans="3:27">
-      <c r="C20" s="6">
+    <row r="20" s="4" customFormat="1" ht="17" customHeight="1" spans="3:27">
+      <c r="C20" s="4">
         <v>15</v>
       </c>
-      <c r="D20" s="6">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1</v>
-      </c>
-      <c r="F20" s="6">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4">
         <v>3008</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="J20" s="7">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6">
-        <v>0</v>
-      </c>
-      <c r="L20" s="6">
-        <v>0</v>
-      </c>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6">
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4">
         <v>3</v>
       </c>
-      <c r="O20" s="6">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="6">
-        <v>0</v>
-      </c>
-      <c r="V20" s="6">
-        <v>0</v>
-      </c>
-      <c r="W20" s="6">
-        <v>0</v>
-      </c>
-      <c r="X20" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="6" customFormat="1" ht="17" customHeight="1" spans="3:27">
-      <c r="C21" s="6">
+      <c r="O20" s="4">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4">
+        <v>0</v>
+      </c>
+      <c r="V20" s="4">
+        <v>0</v>
+      </c>
+      <c r="W20" s="4">
+        <v>0</v>
+      </c>
+      <c r="X20" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" ht="17" customHeight="1" spans="3:27">
+      <c r="C21" s="4">
         <v>16</v>
       </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1</v>
-      </c>
-      <c r="G21" s="7">
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1</v>
+      </c>
+      <c r="G21" s="4">
         <v>1009</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="J21" s="7">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6">
-        <v>0</v>
-      </c>
-      <c r="O21" s="6">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6">
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4">
         <v>3</v>
       </c>
-      <c r="S21" s="6">
-        <v>0</v>
-      </c>
-      <c r="T21" s="6">
-        <v>0</v>
-      </c>
-      <c r="U21" s="6">
-        <v>0</v>
-      </c>
-      <c r="V21" s="6">
-        <v>0</v>
-      </c>
-      <c r="W21" s="6">
-        <v>0</v>
-      </c>
-      <c r="X21" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="6">
+      <c r="S21" s="4">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4">
+        <v>0</v>
+      </c>
+      <c r="W21" s="4">
+        <v>0</v>
+      </c>
+      <c r="X21" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="4">
         <v>109</v>
       </c>
     </row>
-    <row r="22" s="6" customFormat="1" ht="17" customHeight="1" spans="3:27">
-      <c r="C22" s="6">
+    <row r="22" s="4" customFormat="1" ht="17" customHeight="1" spans="3:27">
+      <c r="C22" s="4">
         <v>17</v>
       </c>
-      <c r="D22" s="6">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1</v>
-      </c>
-      <c r="F22" s="6">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7">
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="4">
         <v>2009</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="J22" s="7">
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
-        <v>0</v>
-      </c>
-      <c r="L22" s="6">
-        <v>0</v>
-      </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6">
-        <v>0</v>
-      </c>
-      <c r="O22" s="6">
-        <v>0</v>
-      </c>
-      <c r="P22" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="6">
-        <v>0</v>
-      </c>
-      <c r="T22" s="6">
-        <v>50</v>
-      </c>
-      <c r="U22" s="6">
-        <v>0</v>
-      </c>
-      <c r="V22" s="6">
-        <v>0</v>
-      </c>
-      <c r="W22" s="6">
-        <v>0</v>
-      </c>
-      <c r="X22" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="6" customFormat="1" ht="17" customHeight="1" spans="3:27">
-      <c r="C23" s="6">
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4">
+        <v>0</v>
+      </c>
+      <c r="P22" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4">
+        <v>50</v>
+      </c>
+      <c r="U22" s="4">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4">
+        <v>0</v>
+      </c>
+      <c r="W22" s="4">
+        <v>0</v>
+      </c>
+      <c r="X22" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="1" ht="17" customHeight="1" spans="3:27">
+      <c r="C23" s="4">
         <v>18</v>
       </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1</v>
-      </c>
-      <c r="F23" s="6">
-        <v>1</v>
-      </c>
-      <c r="G23" s="7">
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4">
         <v>3009</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="J23" s="7">
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6">
-        <v>0</v>
-      </c>
-      <c r="O23" s="6">
+      <c r="J23" s="4">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4">
         <v>2</v>
       </c>
-      <c r="P23" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>0</v>
-      </c>
-      <c r="S23" s="6">
-        <v>0</v>
-      </c>
-      <c r="T23" s="6">
-        <v>0</v>
-      </c>
-      <c r="U23" s="6">
-        <v>0</v>
-      </c>
-      <c r="V23" s="6">
-        <v>0</v>
-      </c>
-      <c r="W23" s="6">
-        <v>0</v>
-      </c>
-      <c r="X23" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C24" s="6">
+      <c r="P23" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>0</v>
+      </c>
+      <c r="R23" s="4">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4">
+        <v>0</v>
+      </c>
+      <c r="U23" s="4">
+        <v>0</v>
+      </c>
+      <c r="V23" s="4">
+        <v>0</v>
+      </c>
+      <c r="W23" s="4">
+        <v>0</v>
+      </c>
+      <c r="X23" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C24" s="4">
         <v>19</v>
       </c>
-      <c r="D24" s="6">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6">
-        <v>1</v>
-      </c>
-      <c r="F24" s="6">
-        <v>1</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4">
         <v>3002</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="J24" s="7">
-        <v>0</v>
-      </c>
-      <c r="K24" s="7">
-        <v>0</v>
-      </c>
-      <c r="L24" s="7">
-        <v>0</v>
-      </c>
-      <c r="M24" s="7">
-        <v>0</v>
-      </c>
-      <c r="N24" s="7">
-        <v>0</v>
-      </c>
-      <c r="O24" s="7">
-        <v>0</v>
-      </c>
-      <c r="P24" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>0</v>
-      </c>
-      <c r="R24" s="7">
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4">
+        <v>0</v>
+      </c>
+      <c r="P24" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>0</v>
+      </c>
+      <c r="R24" s="4">
         <v>20</v>
       </c>
-      <c r="S24" s="7">
-        <v>0</v>
-      </c>
-      <c r="T24" s="7">
-        <v>0</v>
-      </c>
-      <c r="U24" s="7">
-        <v>0</v>
-      </c>
-      <c r="V24" s="7">
-        <v>0</v>
-      </c>
-      <c r="W24" s="7">
-        <v>0</v>
-      </c>
-      <c r="X24" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="6">
+      <c r="S24" s="4">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4">
+        <v>0</v>
+      </c>
+      <c r="W24" s="4">
+        <v>0</v>
+      </c>
+      <c r="X24" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="4">
         <v>101</v>
       </c>
     </row>
-    <row r="25" s="6" customFormat="1" customHeight="1" spans="3:27">
-      <c r="T25" s="7"/>
-    </row>
+    <row r="25" s="4" customFormat="1" customHeight="1"/>
     <row r="26" customHeight="1" spans="3:27">
       <c r="Z26" s="4"/>
     </row>
@@ -12305,10 +12304,10 @@
         <v>6</v>
       </c>
       <c r="E6" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -12323,10 +12322,10 @@
         <v>318</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L6" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -12341,7 +12340,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F7" s="1">
         <v>100</v>
@@ -12356,13 +12355,13 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="L7" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -12377,10 +12376,10 @@
         <v>6</v>
       </c>
       <c r="E8" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -12392,13 +12391,13 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L8" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -12413,10 +12412,10 @@
         <v>6</v>
       </c>
       <c r="E9" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -12428,13 +12427,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L9" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -12452,7 +12451,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -12464,13 +12463,13 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L10" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -12485,10 +12484,10 @@
         <v>6</v>
       </c>
       <c r="E11" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -12500,13 +12499,13 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L11" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -12521,10 +12520,10 @@
         <v>6</v>
       </c>
       <c r="E12" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F12" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -12536,13 +12535,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L12" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -12557,10 +12556,10 @@
         <v>6</v>
       </c>
       <c r="E13" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -12572,13 +12571,13 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L13" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -12593,10 +12592,10 @@
         <v>6</v>
       </c>
       <c r="E14" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F14" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -12608,13 +12607,13 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L14" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -12629,10 +12628,10 @@
         <v>6</v>
       </c>
       <c r="E15" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F15" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -12644,13 +12643,13 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L15" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -12665,10 +12664,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F16" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -12680,13 +12679,13 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L16" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -12701,10 +12700,10 @@
         <v>6</v>
       </c>
       <c r="E17" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -12716,13 +12715,13 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="L17" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M17"/>
       <c r="N17"/>
@@ -12748,7 +12747,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -12763,10 +12762,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -12784,10 +12783,10 @@
         <v>6</v>
       </c>
       <c r="E20" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -12799,10 +12798,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -12824,10 +12823,10 @@
         <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F21" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -12839,10 +12838,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -12860,10 +12859,10 @@
         <v>6</v>
       </c>
       <c r="E22" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F22" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -12875,10 +12874,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -12911,10 +12910,10 @@
         <v>6</v>
       </c>
       <c r="E25" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F25" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G25" s="1">
         <v>2</v>
@@ -12926,10 +12925,10 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L25" s="1">
         <v>50</v>
@@ -12944,7 +12943,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F26" s="1">
         <v>100</v>
@@ -12959,10 +12958,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L26" s="1">
         <v>50</v>
@@ -12980,10 +12979,10 @@
         <v>6</v>
       </c>
       <c r="E27" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F27" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G27" s="1">
         <v>2</v>
@@ -12995,10 +12994,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L27" s="1">
         <v>50</v>
@@ -13016,10 +13015,10 @@
         <v>6</v>
       </c>
       <c r="E28" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F28" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G28" s="1">
         <v>2</v>
@@ -13031,10 +13030,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L28" s="1">
         <v>50</v>
@@ -13055,7 +13054,7 @@
         <v>100</v>
       </c>
       <c r="F29" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G29" s="1">
         <v>2</v>
@@ -13067,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L29" s="1">
         <v>50</v>
@@ -13088,10 +13087,10 @@
         <v>6</v>
       </c>
       <c r="E30" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F30" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G30" s="1">
         <v>2</v>
@@ -13103,10 +13102,10 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L30" s="1">
         <v>50</v>
@@ -13124,10 +13123,10 @@
         <v>6</v>
       </c>
       <c r="E31" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F31" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
@@ -13139,10 +13138,10 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L31" s="1">
         <v>50</v>
@@ -13160,10 +13159,10 @@
         <v>6</v>
       </c>
       <c r="E32" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F32" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -13175,10 +13174,10 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L32" s="1">
         <v>50</v>
@@ -13196,10 +13195,10 @@
         <v>6</v>
       </c>
       <c r="E33" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F33" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -13211,10 +13210,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L33" s="1">
         <v>50</v>
@@ -13232,10 +13231,10 @@
         <v>6</v>
       </c>
       <c r="E34" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F34" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G34" s="1">
         <v>2</v>
@@ -13247,10 +13246,10 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L34" s="1">
         <v>50</v>
@@ -13268,10 +13267,10 @@
         <v>6</v>
       </c>
       <c r="E35" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F35" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
@@ -13283,10 +13282,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L35" s="1">
         <v>50</v>
@@ -13304,10 +13303,10 @@
         <v>6</v>
       </c>
       <c r="E36" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F36" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
@@ -13319,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="L36" s="1">
         <v>30</v>
@@ -13345,7 +13344,7 @@
         <v>6</v>
       </c>
       <c r="E38" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F38" s="1">
         <v>20</v>
@@ -13360,10 +13359,10 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O38" s="4"/>
       <c r="P38" s="1">
@@ -13378,10 +13377,10 @@
         <v>6</v>
       </c>
       <c r="E39" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F39" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G39" s="1">
         <v>2</v>
@@ -13393,7 +13392,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>172</v>
@@ -13417,10 +13416,10 @@
         <v>6</v>
       </c>
       <c r="E40" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -13432,10 +13431,10 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L40"/>
       <c r="M40"/>
@@ -13457,10 +13456,10 @@
         <v>6</v>
       </c>
       <c r="E41" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G41" s="1">
         <v>2</v>
@@ -13472,7 +13471,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>297</v>
@@ -13527,10 +13526,10 @@
         <v>6</v>
       </c>
       <c r="E45" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G45" s="1">
         <v>3</v>
@@ -13542,10 +13541,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L45" s="1">
         <v>50</v>
@@ -13563,7 +13562,7 @@
         <v>6</v>
       </c>
       <c r="E46" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F46" s="1">
         <v>100</v>
@@ -13578,10 +13577,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L46" s="1">
         <v>50</v>
@@ -13599,10 +13598,10 @@
         <v>6</v>
       </c>
       <c r="E47" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F47" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G47" s="1">
         <v>3</v>
@@ -13614,10 +13613,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L47" s="1">
         <v>50</v>
@@ -13635,10 +13634,10 @@
         <v>6</v>
       </c>
       <c r="E48" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F48" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G48" s="1">
         <v>3</v>
@@ -13650,10 +13649,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L48" s="1">
         <v>50</v>
@@ -13674,7 +13673,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -13686,10 +13685,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L49" s="1">
         <v>50</v>
@@ -13707,10 +13706,10 @@
         <v>6</v>
       </c>
       <c r="E50" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F50" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G50" s="1">
         <v>3</v>
@@ -13722,10 +13721,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L50" s="1">
         <v>50</v>
@@ -13743,10 +13742,10 @@
         <v>6</v>
       </c>
       <c r="E51" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F51" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -13758,10 +13757,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L51" s="1">
         <v>50</v>
@@ -13779,10 +13778,10 @@
         <v>6</v>
       </c>
       <c r="E52" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F52" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G52" s="1">
         <v>3</v>
@@ -13794,10 +13793,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L52" s="1">
         <v>50</v>
@@ -13815,10 +13814,10 @@
         <v>6</v>
       </c>
       <c r="E53" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F53" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="G53" s="1">
         <v>3</v>
@@ -13830,10 +13829,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L53" s="1">
         <v>50</v>
@@ -13851,10 +13850,10 @@
         <v>6</v>
       </c>
       <c r="E54" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F54" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G54" s="1">
         <v>3</v>
@@ -13866,10 +13865,10 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L54" s="1">
         <v>50</v>
@@ -13887,10 +13886,10 @@
         <v>6</v>
       </c>
       <c r="E55" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F55" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G55" s="1">
         <v>3</v>
@@ -13902,10 +13901,10 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L55" s="1">
         <v>50</v>
@@ -13920,10 +13919,10 @@
         <v>6</v>
       </c>
       <c r="E56" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F56" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G56" s="1">
         <v>3</v>
@@ -13935,10 +13934,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="L56" s="1">
         <v>30</v>
@@ -13980,7 +13979,7 @@
         <v>6</v>
       </c>
       <c r="E59" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F59" s="1">
         <v>20</v>
@@ -13995,10 +13994,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O59" s="4"/>
       <c r="P59" s="1">
@@ -14013,10 +14012,10 @@
         <v>6</v>
       </c>
       <c r="E60" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F60" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G60" s="1">
         <v>3</v>
@@ -14028,10 +14027,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O60" s="4"/>
       <c r="Q60" s="1"/>
@@ -14050,10 +14049,10 @@
         <v>6</v>
       </c>
       <c r="E61" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G61" s="1">
         <v>3</v>
@@ -14065,7 +14064,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>314</v>
